--- a/WalMart coding.xlsx
+++ b/WalMart coding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RaushanKumarManjhi\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.NET-Full-stack-developer-Interview-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A3F218-753E-4E7E-B0B4-C82DE4D0027B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E7ED3-C899-4CA7-A6AD-F210B2EF60CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{1E003D2F-90E0-4701-A326-96A06DB98D7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1E003D2F-90E0-4701-A326-96A06DB98D7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Linq" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="443">
   <si>
     <t>Two Sum</t>
   </si>
@@ -1258,6 +1259,150 @@
   </si>
   <si>
     <t># 🟠 Interview Level</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>LeetCode #</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Left + Right</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>Valid Palindrome II</t>
+  </si>
+  <si>
+    <t>Left + Right + Skip</t>
+  </si>
+  <si>
+    <t>Slow + Fast</t>
+  </si>
+  <si>
+    <t>Reverse Two Pointers</t>
+  </si>
+  <si>
+    <t>Backspace String Compare</t>
+  </si>
+  <si>
+    <t>Two Sum II - Input Array Is Sorted</t>
+  </si>
+  <si>
+    <t>Opposite Direction</t>
+  </si>
+  <si>
+    <t>Linked List Cycle</t>
+  </si>
+  <si>
+    <t>Fast + Slow</t>
+  </si>
+  <si>
+    <t>Middle of the Linked List</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <t>Sort + Two Pointers</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>3Sum Closest</t>
+  </si>
+  <si>
+    <t>4Sum</t>
+  </si>
+  <si>
+    <t>Sort Colors</t>
+  </si>
+  <si>
+    <t>Dutch National Flag</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from Sorted Array II</t>
+  </si>
+  <si>
+    <t>Find the Duplicate Number</t>
+  </si>
+  <si>
+    <t>Linked List Cycle II</t>
+  </si>
+  <si>
+    <t>Odd Even Linked List</t>
+  </si>
+  <si>
+    <t>Linked List Pointers</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from Sorted List II</t>
+  </si>
+  <si>
+    <t>Partition List</t>
+  </si>
+  <si>
+    <t>Rotate List</t>
+  </si>
+  <si>
+    <t>Reorder List</t>
+  </si>
+  <si>
+    <t>Fast + Slow + Reverse</t>
+  </si>
+  <si>
+    <t>Palindrome Linked List</t>
+  </si>
+  <si>
+    <t>Swap Nodes in Pairs</t>
+  </si>
+  <si>
+    <t>Sum of Square Numbers</t>
+  </si>
+  <si>
+    <t>Boats to Save People</t>
+  </si>
+  <si>
+    <t>Interval List Intersections</t>
+  </si>
+  <si>
+    <t>Longest Word in Dictionary Through Deleting</t>
+  </si>
+  <si>
+    <t>Subsequence</t>
+  </si>
+  <si>
+    <t>Bag of Tokens</t>
+  </si>
+  <si>
+    <t>Sort Transformed Array</t>
+  </si>
+  <si>
+    <t>Valid Triangle Number</t>
+  </si>
+  <si>
+    <t>Sorted + Two Pointers</t>
+  </si>
+  <si>
+    <t>3Sum With Multiplicity</t>
+  </si>
+  <si>
+    <t>Longest Mountain in Array</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1576,6 +1721,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1910,12 +2057,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492E94C7-1E50-44A2-8A29-91AA6B3C091C}">
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="62.5703125" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="1" max="1" width="62" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2952,17 +3099,766 @@
       </c>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="2:3">
+    <row r="145" spans="1:5">
       <c r="B145" s="8" t="s">
         <v>275</v>
       </c>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="2:3" ht="15.75" thickBot="1">
+    <row r="146" spans="1:5" ht="15.75" thickBot="1">
       <c r="B146" s="10" t="s">
         <v>276</v>
       </c>
       <c r="C146" s="2"/>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" thickBot="1"/>
+    <row r="150" spans="1:5">
+      <c r="A150" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="B150" s="44" t="s">
+        <v>396</v>
+      </c>
+      <c r="C150" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="D150" s="44" t="s">
+        <v>398</v>
+      </c>
+      <c r="E150" s="35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B151" s="43">
+        <v>344</v>
+      </c>
+      <c r="C151" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D151" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B152" s="43">
+        <v>125</v>
+      </c>
+      <c r="C152" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="D152" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B153" s="43">
+        <v>345</v>
+      </c>
+      <c r="C153" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D153" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B154" s="43">
+        <v>680</v>
+      </c>
+      <c r="C154" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="D154" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B155" s="43">
+        <v>26</v>
+      </c>
+      <c r="C155" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D155" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B156" s="43">
+        <v>27</v>
+      </c>
+      <c r="C156" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B157" s="43">
+        <v>283</v>
+      </c>
+      <c r="C157" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B158" s="43">
+        <v>88</v>
+      </c>
+      <c r="C158" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B159" s="43">
+        <v>977</v>
+      </c>
+      <c r="C159" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D159" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B160" s="43">
+        <v>905</v>
+      </c>
+      <c r="C160" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B161" s="43">
+        <v>1089</v>
+      </c>
+      <c r="C161" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B162" s="43">
+        <v>844</v>
+      </c>
+      <c r="C162" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="D162" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B163" s="43">
+        <v>392</v>
+      </c>
+      <c r="C163" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D163" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B164" s="43">
+        <v>167</v>
+      </c>
+      <c r="C164" s="43" t="s">
+        <v>407</v>
+      </c>
+      <c r="D164" s="43" t="s">
+        <v>408</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B165" s="43">
+        <v>349</v>
+      </c>
+      <c r="C165" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B166" s="43">
+        <v>350</v>
+      </c>
+      <c r="C166" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B167" s="43">
+        <v>141</v>
+      </c>
+      <c r="C167" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="D167" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B168" s="43">
+        <v>876</v>
+      </c>
+      <c r="C168" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="D168" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B169" s="43">
+        <v>19</v>
+      </c>
+      <c r="C169" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="D169" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B170" s="43">
+        <v>15</v>
+      </c>
+      <c r="C170" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="D170" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B171" s="43">
+        <v>11</v>
+      </c>
+      <c r="C171" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="D171" s="43" t="s">
+        <v>408</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B172" s="43">
+        <v>16</v>
+      </c>
+      <c r="C172" s="43" t="s">
+        <v>416</v>
+      </c>
+      <c r="D172" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B173" s="43">
+        <v>18</v>
+      </c>
+      <c r="C173" s="43" t="s">
+        <v>417</v>
+      </c>
+      <c r="D173" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B174" s="43">
+        <v>75</v>
+      </c>
+      <c r="C174" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="D174" s="43" t="s">
+        <v>419</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B175" s="43">
+        <v>80</v>
+      </c>
+      <c r="C175" s="43" t="s">
+        <v>420</v>
+      </c>
+      <c r="D175" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B176" s="43">
+        <v>287</v>
+      </c>
+      <c r="C176" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="D176" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B177" s="43">
+        <v>142</v>
+      </c>
+      <c r="C177" s="43" t="s">
+        <v>422</v>
+      </c>
+      <c r="D177" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B178" s="43">
+        <v>328</v>
+      </c>
+      <c r="C178" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="D178" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B179" s="43">
+        <v>82</v>
+      </c>
+      <c r="C179" s="43" t="s">
+        <v>425</v>
+      </c>
+      <c r="D179" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B180" s="43">
+        <v>86</v>
+      </c>
+      <c r="C180" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="D180" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B181" s="43">
+        <v>61</v>
+      </c>
+      <c r="C181" s="43" t="s">
+        <v>427</v>
+      </c>
+      <c r="D181" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B182" s="43">
+        <v>143</v>
+      </c>
+      <c r="C182" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D182" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B183" s="43">
+        <v>234</v>
+      </c>
+      <c r="C183" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="D183" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B184" s="43">
+        <v>24</v>
+      </c>
+      <c r="C184" s="43" t="s">
+        <v>431</v>
+      </c>
+      <c r="D184" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B185" s="43">
+        <v>633</v>
+      </c>
+      <c r="C185" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="D185" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B186" s="43">
+        <v>881</v>
+      </c>
+      <c r="C186" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="D186" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B187" s="43">
+        <v>986</v>
+      </c>
+      <c r="C187" s="43" t="s">
+        <v>434</v>
+      </c>
+      <c r="D187" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B188" s="43">
+        <v>524</v>
+      </c>
+      <c r="C188" s="43" t="s">
+        <v>435</v>
+      </c>
+      <c r="D188" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B189" s="43">
+        <v>948</v>
+      </c>
+      <c r="C189" s="43" t="s">
+        <v>437</v>
+      </c>
+      <c r="D189" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B190" s="43">
+        <v>360</v>
+      </c>
+      <c r="C190" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="D190" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B191" s="43">
+        <v>611</v>
+      </c>
+      <c r="C191" s="43" t="s">
+        <v>439</v>
+      </c>
+      <c r="D191" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B192" s="43">
+        <v>923</v>
+      </c>
+      <c r="C192" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="D192" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A193" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B193" s="11">
+        <v>845</v>
+      </c>
+      <c r="C193" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>401</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WalMart coding.xlsx
+++ b/WalMart coding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.NET-Full-stack-developer-Interview-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E5F7AB-F565-4CE4-9D64-25973B389954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8728D407-F829-4CD1-A174-22F581E0CDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{1E003D2F-90E0-4701-A326-96A06DB98D7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="7" xr2:uid="{1E003D2F-90E0-4701-A326-96A06DB98D7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="C# Interview Traps(Rivision)" sheetId="7" r:id="rId5"/>
     <sheet name="C# interview Chapter-wise list" sheetId="8" r:id="rId6"/>
     <sheet name="Logic building" sheetId="2" r:id="rId7"/>
-    <sheet name="System Design" sheetId="9" r:id="rId8"/>
-    <sheet name="Linq" sheetId="4" r:id="rId9"/>
+    <sheet name="SQL_Syllabus&amp;Problems" sheetId="11" r:id="rId8"/>
+    <sheet name="System Design" sheetId="9" r:id="rId9"/>
+    <sheet name="Linq" sheetId="4" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="1748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="2406">
   <si>
     <t>Two Sum</t>
   </si>
@@ -7375,12 +7376,2217 @@
   <si>
     <t>C# → .NET Fundamentals → ASP.NET Core → Web API → DI/Middleware → EF Core → Security → Async → Caching → Testing → Clean Architecture → Docker → Azure → Microservices → Distributed Systems → System Design.</t>
   </si>
+  <si>
+    <t>SQL Server — Phase-wise Syllabus</t>
+  </si>
+  <si>
+    <t>Phase 1 — SQL Fundamentals</t>
+  </si>
+  <si>
+    <t>1. What is SQL?</t>
+  </si>
+  <si>
+    <t>2. SQL vs SQL Server</t>
+  </si>
+  <si>
+    <t>3. Database</t>
+  </si>
+  <si>
+    <t>4. Schema</t>
+  </si>
+  <si>
+    <t>5. Table</t>
+  </si>
+  <si>
+    <t>6. Row</t>
+  </si>
+  <si>
+    <t>7. Column</t>
+  </si>
+  <si>
+    <t>8. Primary Key</t>
+  </si>
+  <si>
+    <t>9. Foreign Key</t>
+  </si>
+  <si>
+    <t>10. Constraints</t>
+  </si>
+  <si>
+    <t>11. NULL</t>
+  </si>
+  <si>
+    <t>12. NOT NULL</t>
+  </si>
+  <si>
+    <t>13. DEFAULT</t>
+  </si>
+  <si>
+    <t>14. UNIQUE</t>
+  </si>
+  <si>
+    <t>15. CHECK</t>
+  </si>
+  <si>
+    <t>16. IDENTITY</t>
+  </si>
+  <si>
+    <t>Phase 2 — Data Types</t>
+  </si>
+  <si>
+    <t>1. INT</t>
+  </si>
+  <si>
+    <t>2. BIGINT</t>
+  </si>
+  <si>
+    <t>3. SMALLINT</t>
+  </si>
+  <si>
+    <t>4. TINYINT</t>
+  </si>
+  <si>
+    <t>5. DECIMAL</t>
+  </si>
+  <si>
+    <t>6. NUMERIC</t>
+  </si>
+  <si>
+    <t>7. FLOAT</t>
+  </si>
+  <si>
+    <t>8. REAL</t>
+  </si>
+  <si>
+    <t>9. CHAR</t>
+  </si>
+  <si>
+    <t>10. VARCHAR</t>
+  </si>
+  <si>
+    <t>11. NCHAR</t>
+  </si>
+  <si>
+    <t>12. NVARCHAR</t>
+  </si>
+  <si>
+    <t>13. DATE</t>
+  </si>
+  <si>
+    <t>14. DATETIME</t>
+  </si>
+  <si>
+    <t>15. DATETIME2</t>
+  </si>
+  <si>
+    <t>16. TIME</t>
+  </si>
+  <si>
+    <t>17. BIT</t>
+  </si>
+  <si>
+    <t>18. UNIQUEIDENTIFIER</t>
+  </si>
+  <si>
+    <t>19. XML</t>
+  </si>
+  <si>
+    <t>20. JSON</t>
+  </si>
+  <si>
+    <t>Interview Traps</t>
+  </si>
+  <si>
+    <r>
+      <t>CHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DATETIME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DATETIME2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FLOAT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BIGINT</t>
+    </r>
+  </si>
+  <si>
+    <t>Phase 3 — SELECT Queries</t>
+  </si>
+  <si>
+    <t>1. SELECT</t>
+  </si>
+  <si>
+    <t>2. FROM</t>
+  </si>
+  <si>
+    <t>3. WHERE</t>
+  </si>
+  <si>
+    <t>4. DISTINCT</t>
+  </si>
+  <si>
+    <t>5. TOP</t>
+  </si>
+  <si>
+    <t>6. ORDER BY</t>
+  </si>
+  <si>
+    <t>7. OFFSET</t>
+  </si>
+  <si>
+    <t>8. FETCH</t>
+  </si>
+  <si>
+    <t>9. Column Alias</t>
+  </si>
+  <si>
+    <t>10. Expressions</t>
+  </si>
+  <si>
+    <t>11. CASE</t>
+  </si>
+  <si>
+    <r>
+      <t>12. NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> handling</t>
+    </r>
+  </si>
+  <si>
+    <t>13. IS NULL</t>
+  </si>
+  <si>
+    <t>14. IS NOT NULL</t>
+  </si>
+  <si>
+    <t>Phase 4 — Operators</t>
+  </si>
+  <si>
+    <t>1. Arithmetic Operators</t>
+  </si>
+  <si>
+    <t>2. Comparison Operators</t>
+  </si>
+  <si>
+    <t>3. Logical Operators</t>
+  </si>
+  <si>
+    <t>4. AND</t>
+  </si>
+  <si>
+    <t>5. OR</t>
+  </si>
+  <si>
+    <t>6. NOT</t>
+  </si>
+  <si>
+    <t>7. IN</t>
+  </si>
+  <si>
+    <t>8. NOT IN</t>
+  </si>
+  <si>
+    <t>9. BETWEEN</t>
+  </si>
+  <si>
+    <t>10. LIKE</t>
+  </si>
+  <si>
+    <t>11. Wildcards</t>
+  </si>
+  <si>
+    <t>12. EXISTS</t>
+  </si>
+  <si>
+    <t>13. ANY</t>
+  </si>
+  <si>
+    <t>14. ALL</t>
+  </si>
+  <si>
+    <t>Phase 5 — CRUD</t>
+  </si>
+  <si>
+    <t>1. INSERT</t>
+  </si>
+  <si>
+    <t>2. UPDATE</t>
+  </si>
+  <si>
+    <t>3. DELETE</t>
+  </si>
+  <si>
+    <t>4. TRUNCATE</t>
+  </si>
+  <si>
+    <t>5. MERGE</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>TRUNCATE</t>
+  </si>
+  <si>
+    <t>DROP</t>
+  </si>
+  <si>
+    <t>Difference must be crystal clear.</t>
+  </si>
+  <si>
+    <t>Phase 6 — Functions</t>
+  </si>
+  <si>
+    <t>String Functions</t>
+  </si>
+  <si>
+    <t>1. LEN</t>
+  </si>
+  <si>
+    <t>2. LEFT</t>
+  </si>
+  <si>
+    <t>3. RIGHT</t>
+  </si>
+  <si>
+    <t>4. SUBSTRING</t>
+  </si>
+  <si>
+    <t>5. CHARINDEX</t>
+  </si>
+  <si>
+    <t>6. REPLACE</t>
+  </si>
+  <si>
+    <t>7. UPPER</t>
+  </si>
+  <si>
+    <t>8. LOWER</t>
+  </si>
+  <si>
+    <t>9. TRIM</t>
+  </si>
+  <si>
+    <t>10. CONCAT</t>
+  </si>
+  <si>
+    <t>Date Functions</t>
+  </si>
+  <si>
+    <t>11. GETDATE</t>
+  </si>
+  <si>
+    <t>12. SYSDATETIME</t>
+  </si>
+  <si>
+    <t>13. DATEADD</t>
+  </si>
+  <si>
+    <t>14. DATEDIFF</t>
+  </si>
+  <si>
+    <t>15. DATEPART</t>
+  </si>
+  <si>
+    <t>16. DATENAME</t>
+  </si>
+  <si>
+    <t>17. EOMONTH</t>
+  </si>
+  <si>
+    <t>Numeric</t>
+  </si>
+  <si>
+    <t>18. ROUND</t>
+  </si>
+  <si>
+    <t>19. CEILING</t>
+  </si>
+  <si>
+    <t>20. FLOOR</t>
+  </si>
+  <si>
+    <t>21. ABS</t>
+  </si>
+  <si>
+    <t>Phase 7 — Aggregate Functions</t>
+  </si>
+  <si>
+    <t>1. COUNT</t>
+  </si>
+  <si>
+    <t>2. SUM</t>
+  </si>
+  <si>
+    <t>3. AVG</t>
+  </si>
+  <si>
+    <t>4. MIN</t>
+  </si>
+  <si>
+    <t>5. MAX</t>
+  </si>
+  <si>
+    <t>6. GROUP BY</t>
+  </si>
+  <si>
+    <t>7. HAVING</t>
+  </si>
+  <si>
+    <t>Must understand</t>
+  </si>
+  <si>
+    <t>WHERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ↓</t>
+  </si>
+  <si>
+    <t>GROUP BY</t>
+  </si>
+  <si>
+    <t>HAVING</t>
+  </si>
+  <si>
+    <t>and actual SQL logical processing order.</t>
+  </si>
+  <si>
+    <t>Phase 8 — Joins</t>
+  </si>
+  <si>
+    <t>🔥🔥 Very important.</t>
+  </si>
+  <si>
+    <t>1. INNER JOIN</t>
+  </si>
+  <si>
+    <t>2. LEFT JOIN</t>
+  </si>
+  <si>
+    <t>3. RIGHT JOIN</t>
+  </si>
+  <si>
+    <t>4. FULL OUTER JOIN</t>
+  </si>
+  <si>
+    <t>5. CROSS JOIN</t>
+  </si>
+  <si>
+    <t>6. SELF JOIN</t>
+  </si>
+  <si>
+    <t>INNER vs LEFT JOIN</t>
+  </si>
+  <si>
+    <t>LEFT JOIN + WHERE condition</t>
+  </si>
+  <si>
+    <t>SELF JOIN</t>
+  </si>
+  <si>
+    <t>Multiple JOINs</t>
+  </si>
+  <si>
+    <t>JOIN vs EXISTS</t>
+  </si>
+  <si>
+    <t>Phase 9 — Subqueries</t>
+  </si>
+  <si>
+    <t>1. Subquery</t>
+  </si>
+  <si>
+    <t>2. Scalar Subquery</t>
+  </si>
+  <si>
+    <t>3. Single-row Subquery</t>
+  </si>
+  <si>
+    <t>4. Multi-row Subquery</t>
+  </si>
+  <si>
+    <t>5. Correlated Subquery</t>
+  </si>
+  <si>
+    <t>6. Nested Subquery</t>
+  </si>
+  <si>
+    <t>7. EXISTS</t>
+  </si>
+  <si>
+    <t>8. NOT EXISTS</t>
+  </si>
+  <si>
+    <t>9. Subquery vs JOIN</t>
+  </si>
+  <si>
+    <t>Phase 10 — Set Operators</t>
+  </si>
+  <si>
+    <t>1. UNION</t>
+  </si>
+  <si>
+    <t>2. UNION ALL</t>
+  </si>
+  <si>
+    <t>3. INTERSECT</t>
+  </si>
+  <si>
+    <t>4. EXCEPT</t>
+  </si>
+  <si>
+    <t>Understand:</t>
+  </si>
+  <si>
+    <t>UNION</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
+    <t>UNION ALL</t>
+  </si>
+  <si>
+    <t>especially performance.</t>
+  </si>
+  <si>
+    <t>Phase 11 — CTE &amp; Temporary Objects</t>
+  </si>
+  <si>
+    <t>1. CTE</t>
+  </si>
+  <si>
+    <t>2. Recursive CTE</t>
+  </si>
+  <si>
+    <t>3. Temporary Table</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Local Temp Table </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#Table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Global Temp Table </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>##Table</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Table Variable</t>
+  </si>
+  <si>
+    <t>7. CTE vs Temp Table</t>
+  </si>
+  <si>
+    <t>8. Temp Table vs Table Variable</t>
+  </si>
+  <si>
+    <t>9. Derived Table</t>
+  </si>
+  <si>
+    <t>Phase 12 — Views</t>
+  </si>
+  <si>
+    <t>1. What is View?</t>
+  </si>
+  <si>
+    <t>2. Create View</t>
+  </si>
+  <si>
+    <t>3. Alter View</t>
+  </si>
+  <si>
+    <t>4. Drop View</t>
+  </si>
+  <si>
+    <t>5. View vs Table</t>
+  </si>
+  <si>
+    <t>6. View vs Stored Procedure</t>
+  </si>
+  <si>
+    <t>7. Updatable View</t>
+  </si>
+  <si>
+    <t>8. Indexed View</t>
+  </si>
+  <si>
+    <t>Phase 13 — Stored Procedures</t>
+  </si>
+  <si>
+    <t>🔥🔥 Important for .NET interviews.</t>
+  </si>
+  <si>
+    <t>1. Stored Procedure</t>
+  </si>
+  <si>
+    <t>2. Create Procedure</t>
+  </si>
+  <si>
+    <t>3. Input Parameters</t>
+  </si>
+  <si>
+    <t>4. Output Parameters</t>
+  </si>
+  <si>
+    <t>5. Return Value</t>
+  </si>
+  <si>
+    <t>6. Default Parameters</t>
+  </si>
+  <si>
+    <t>7. Procedure with multiple queries</t>
+  </si>
+  <si>
+    <t>8. Temporary tables inside SP</t>
+  </si>
+  <si>
+    <t>9. Dynamic SQL</t>
+  </si>
+  <si>
+    <t>10. sp_executesql</t>
+  </si>
+  <si>
+    <t>11. Stored Procedure vs Function</t>
+  </si>
+  <si>
+    <t>Phase 14 — Functions</t>
+  </si>
+  <si>
+    <t>1. Scalar Function</t>
+  </si>
+  <si>
+    <t>2. Inline Table-Valued Function</t>
+  </si>
+  <si>
+    <t>3. Multi-Statement Table-Valued Function</t>
+  </si>
+  <si>
+    <t>4. User Defined Functions</t>
+  </si>
+  <si>
+    <t>5. Function vs Stored Procedure</t>
+  </si>
+  <si>
+    <t>6. UDF Performance</t>
+  </si>
+  <si>
+    <t>Phase 15 — Indexing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔥🔥🔥 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5+ years ke liye extremely important.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. What is Index?</t>
+  </si>
+  <si>
+    <t>2. Clustered Index</t>
+  </si>
+  <si>
+    <t>3. Non-Clustered Index</t>
+  </si>
+  <si>
+    <t>4. Clustered vs Non-Clustered</t>
+  </si>
+  <si>
+    <t>5. Composite Index</t>
+  </si>
+  <si>
+    <t>6. Unique Index</t>
+  </si>
+  <si>
+    <t>7. Filtered Index</t>
+  </si>
+  <si>
+    <t>8. Covering Index</t>
+  </si>
+  <si>
+    <t>9. Included Columns</t>
+  </si>
+  <si>
+    <t>10. Index Seek</t>
+  </si>
+  <si>
+    <t>11. Index Scan</t>
+  </si>
+  <si>
+    <t>12. Table Scan</t>
+  </si>
+  <si>
+    <t>13. Key Lookup</t>
+  </si>
+  <si>
+    <t>14. Index Fragmentation</t>
+  </si>
+  <si>
+    <t>15. Fill Factor</t>
+  </si>
+  <si>
+    <t>16. Rebuild Index</t>
+  </si>
+  <si>
+    <t>17. Reorganize Index</t>
+  </si>
+  <si>
+    <t>18. Missing Index</t>
+  </si>
+  <si>
+    <t>19. Over-indexing</t>
+  </si>
+  <si>
+    <t>Phase 16 — Query Execution &amp; Optimization</t>
+  </si>
+  <si>
+    <t>🔥🔥🔥 Senior-level.</t>
+  </si>
+  <si>
+    <t>1. Execution Plan</t>
+  </si>
+  <si>
+    <t>2. Estimated Execution Plan</t>
+  </si>
+  <si>
+    <t>3. Actual Execution Plan</t>
+  </si>
+  <si>
+    <t>4. Query Cost</t>
+  </si>
+  <si>
+    <t>5. Index Seek vs Scan</t>
+  </si>
+  <si>
+    <t>6. Key Lookup</t>
+  </si>
+  <si>
+    <t>7. Join Algorithms</t>
+  </si>
+  <si>
+    <t>8. Nested Loop</t>
+  </si>
+  <si>
+    <t>9. Hash Join</t>
+  </si>
+  <si>
+    <t>10. Merge Join</t>
+  </si>
+  <si>
+    <t>11. Sort Operator</t>
+  </si>
+  <si>
+    <t>12. Filter Operator</t>
+  </si>
+  <si>
+    <t>13. Statistics</t>
+  </si>
+  <si>
+    <t>14. Cardinality Estimation</t>
+  </si>
+  <si>
+    <t>15. SARGable Queries</t>
+  </si>
+  <si>
+    <t>16. Parameter Sniffing</t>
+  </si>
+  <si>
+    <t>17. Query Optimization</t>
+  </si>
+  <si>
+    <t>18. Query Store</t>
+  </si>
+  <si>
+    <t>Phase 17 — Transactions</t>
+  </si>
+  <si>
+    <t>1. Transaction</t>
+  </si>
+  <si>
+    <t>2. BEGIN TRAN</t>
+  </si>
+  <si>
+    <t>3. COMMIT</t>
+  </si>
+  <si>
+    <t>4. ROLLBACK</t>
+  </si>
+  <si>
+    <t>5. SAVE TRANSACTION</t>
+  </si>
+  <si>
+    <t>6. ACID</t>
+  </si>
+  <si>
+    <t>7. Atomicity</t>
+  </si>
+  <si>
+    <t>8. Consistency</t>
+  </si>
+  <si>
+    <t>9. Isolation</t>
+  </si>
+  <si>
+    <t>10. Durability</t>
+  </si>
+  <si>
+    <t>Phase 18 — Isolation Levels &amp; Concurrency</t>
+  </si>
+  <si>
+    <t>1. Dirty Read</t>
+  </si>
+  <si>
+    <t>2. Non-Repeatable Read</t>
+  </si>
+  <si>
+    <t>3. Phantom Read</t>
+  </si>
+  <si>
+    <t>4. Lost Update</t>
+  </si>
+  <si>
+    <t>5. Read Uncommitted</t>
+  </si>
+  <si>
+    <t>6. Read Committed</t>
+  </si>
+  <si>
+    <t>7. Repeatable Read</t>
+  </si>
+  <si>
+    <t>8. Serializable</t>
+  </si>
+  <si>
+    <t>9. Snapshot</t>
+  </si>
+  <si>
+    <t>10. Read Committed Snapshot</t>
+  </si>
+  <si>
+    <t>11. Optimistic Concurrency</t>
+  </si>
+  <si>
+    <t>12. Pessimistic Concurrency</t>
+  </si>
+  <si>
+    <t>Phase 19 — Locks &amp; Deadlocks</t>
+  </si>
+  <si>
+    <t>1. Shared Lock</t>
+  </si>
+  <si>
+    <t>2. Exclusive Lock</t>
+  </si>
+  <si>
+    <t>3. Update Lock</t>
+  </si>
+  <si>
+    <t>4. Intent Lock</t>
+  </si>
+  <si>
+    <t>5. Row Lock</t>
+  </si>
+  <si>
+    <t>6. Page Lock</t>
+  </si>
+  <si>
+    <t>7. Table Lock</t>
+  </si>
+  <si>
+    <t>8. Lock Escalation</t>
+  </si>
+  <si>
+    <t>9. Blocking</t>
+  </si>
+  <si>
+    <t>10. Deadlock</t>
+  </si>
+  <si>
+    <t>11. Deadlock Detection</t>
+  </si>
+  <si>
+    <t>12. Deadlock Prevention</t>
+  </si>
+  <si>
+    <t>13. NOLOCK</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">14. Why </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>NOLOCK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> can be dangerous</t>
+    </r>
+  </si>
+  <si>
+    <t>Phase 20 — SQL Server Performance</t>
+  </si>
+  <si>
+    <t>1. Slow Query Analysis</t>
+  </si>
+  <si>
+    <t>2. Execution Plan Analysis</t>
+  </si>
+  <si>
+    <t>3. Index Optimization</t>
+  </si>
+  <si>
+    <t>4. Statistics</t>
+  </si>
+  <si>
+    <t>5. Query Store</t>
+  </si>
+  <si>
+    <t>6. Blocking Analysis</t>
+  </si>
+  <si>
+    <t>7. Deadlock Analysis</t>
+  </si>
+  <si>
+    <t>8. Connection Issues</t>
+  </si>
+  <si>
+    <t>9. Parameter Sniffing</t>
+  </si>
+  <si>
+    <t>10. N+1 Query Problem</t>
+  </si>
+  <si>
+    <t>11. Pagination Optimization</t>
+  </si>
+  <si>
+    <t>12. Large Table Optimization</t>
+  </si>
+  <si>
+    <t>13. Batch Processing</t>
+  </si>
+  <si>
+    <t>14. Bulk Insert</t>
+  </si>
+  <si>
+    <t>15. Data Archiving</t>
+  </si>
+  <si>
+    <t>Phase 21 — Advanced SQL</t>
+  </si>
+  <si>
+    <t>1. Window Functions</t>
+  </si>
+  <si>
+    <t>2. ROW_NUMBER</t>
+  </si>
+  <si>
+    <t>3. RANK</t>
+  </si>
+  <si>
+    <t>4. DENSE_RANK</t>
+  </si>
+  <si>
+    <t>5. NTILE</t>
+  </si>
+  <si>
+    <t>6. LAG</t>
+  </si>
+  <si>
+    <t>7. LEAD</t>
+  </si>
+  <si>
+    <t>8. FIRST_VALUE</t>
+  </si>
+  <si>
+    <t>9. LAST_VALUE</t>
+  </si>
+  <si>
+    <t>10. OVER()</t>
+  </si>
+  <si>
+    <t>11. PARTITION BY</t>
+  </si>
+  <si>
+    <t>🔥 Practice:</t>
+  </si>
+  <si>
+    <t>Second highest salary</t>
+  </si>
+  <si>
+    <t>Top N per group</t>
+  </si>
+  <si>
+    <t>Running total</t>
+  </si>
+  <si>
+    <t>Duplicate detection</t>
+  </si>
+  <si>
+    <t>Gaps and Islands</t>
+  </si>
+  <si>
+    <t>Previous/Next record</t>
+  </si>
+  <si>
+    <t>Phase 22 — Advanced Database Design</t>
+  </si>
+  <si>
+    <t>1. Database Normalization</t>
+  </si>
+  <si>
+    <t>2. 1NF</t>
+  </si>
+  <si>
+    <t>3. 2NF</t>
+  </si>
+  <si>
+    <t>4. 3NF</t>
+  </si>
+  <si>
+    <t>5. BCNF</t>
+  </si>
+  <si>
+    <t>6. Denormalization</t>
+  </si>
+  <si>
+    <t>7. Normalization vs Denormalization</t>
+  </si>
+  <si>
+    <t>8. Primary Key Design</t>
+  </si>
+  <si>
+    <t>9. Surrogate Key</t>
+  </si>
+  <si>
+    <t>10. Natural Key</t>
+  </si>
+  <si>
+    <t>11. Composite Key</t>
+  </si>
+  <si>
+    <t>12. Referential Integrity</t>
+  </si>
+  <si>
+    <t>13. Cascading</t>
+  </si>
+  <si>
+    <t>14. Soft Delete</t>
+  </si>
+  <si>
+    <t>15. Audit Columns</t>
+  </si>
+  <si>
+    <t>Phase 23 — SQL + .NET / EF Core</t>
+  </si>
+  <si>
+    <t>1. ADO.NET</t>
+  </si>
+  <si>
+    <t>2. SqlConnection</t>
+  </si>
+  <si>
+    <t>3. SqlCommand</t>
+  </si>
+  <si>
+    <t>4. SqlDataReader</t>
+  </si>
+  <si>
+    <t>5. SqlDataAdapter</t>
+  </si>
+  <si>
+    <t>6. Parameterized Queries</t>
+  </si>
+  <si>
+    <t>7. SQL Injection</t>
+  </si>
+  <si>
+    <t>8. Stored Procedure from .NET</t>
+  </si>
+  <si>
+    <t>9. EF Core</t>
+  </si>
+  <si>
+    <t>10. DbContext</t>
+  </si>
+  <si>
+    <t>11. LINQ → SQL translation</t>
+  </si>
+  <si>
+    <r>
+      <t>12. IQueryable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>IEnumerable</t>
+    </r>
+  </si>
+  <si>
+    <t>13. Tracking vs NoTracking</t>
+  </si>
+  <si>
+    <t>14. Include</t>
+  </si>
+  <si>
+    <t>15. Projection</t>
+  </si>
+  <si>
+    <t>16. EF Core Transactions</t>
+  </si>
+  <si>
+    <t>17. Optimistic Concurrency</t>
+  </si>
+  <si>
+    <t>18. Raw SQL</t>
+  </si>
+  <si>
+    <t>19. Stored Procedures with EF Core</t>
+  </si>
+  <si>
+    <t>20. Connection Pooling</t>
+  </si>
+  <si>
+    <t>Phase 24 — Database Architecture &amp; Scaling</t>
+  </si>
+  <si>
+    <t>🔥🔥 Senior/Architect.</t>
+  </si>
+  <si>
+    <t>1. Vertical Scaling</t>
+  </si>
+  <si>
+    <t>2. Horizontal Scaling</t>
+  </si>
+  <si>
+    <t>3. Read Replica</t>
+  </si>
+  <si>
+    <t>4. Database Replication</t>
+  </si>
+  <si>
+    <t>5. Partitioning</t>
+  </si>
+  <si>
+    <t>6. Table Partitioning</t>
+  </si>
+  <si>
+    <t>7. Sharding</t>
+  </si>
+  <si>
+    <t>8. Database per Service</t>
+  </si>
+  <si>
+    <t>9. Multi-Tenant Database</t>
+  </si>
+  <si>
+    <t>10. Multi-Region Database</t>
+  </si>
+  <si>
+    <t>11. Failover</t>
+  </si>
+  <si>
+    <t>12. High Availability</t>
+  </si>
+  <si>
+    <t>13. Disaster Recovery</t>
+  </si>
+  <si>
+    <t>14. Backup</t>
+  </si>
+  <si>
+    <t>15. Restore</t>
+  </si>
+  <si>
+    <t>16. Point-in-Time Recovery</t>
+  </si>
+  <si>
+    <t>Phase 25 — Production-Level SQL Server</t>
+  </si>
+  <si>
+    <t>1. Backup Types</t>
+  </si>
+  <si>
+    <t>2. Full Backup</t>
+  </si>
+  <si>
+    <t>3. Differential Backup</t>
+  </si>
+  <si>
+    <t>4. Transaction Log Backup</t>
+  </si>
+  <si>
+    <t>5. Recovery Models</t>
+  </si>
+  <si>
+    <t>6. Simple</t>
+  </si>
+  <si>
+    <t>7. Full</t>
+  </si>
+  <si>
+    <t>8. Bulk-Logged</t>
+  </si>
+  <si>
+    <t>9. Restore Strategy</t>
+  </si>
+  <si>
+    <t>10. Log Management</t>
+  </si>
+  <si>
+    <t>11. Database Health</t>
+  </si>
+  <si>
+    <t>12. Monitoring</t>
+  </si>
+  <si>
+    <t>13. SQL Agent</t>
+  </si>
+  <si>
+    <t>14. Jobs</t>
+  </si>
+  <si>
+    <t>15. Alerts</t>
+  </si>
+  <si>
+    <t>16. Maintenance Plans</t>
+  </si>
+  <si>
+    <t>17. Security</t>
+  </si>
+  <si>
+    <t>18. Users</t>
+  </si>
+  <si>
+    <t>19. Roles</t>
+  </si>
+  <si>
+    <t>20. Permissions</t>
+  </si>
+  <si>
+    <t>🎯 Tumhare 5+ Years Interview ke liye Priority</t>
+  </si>
+  <si>
+    <t>SQL Basics</t>
+  </si>
+  <si>
+    <t>Joins</t>
+  </si>
+  <si>
+    <t>Subqueries</t>
+  </si>
+  <si>
+    <t>CTE</t>
+  </si>
+  <si>
+    <t>Group By / Having</t>
+  </si>
+  <si>
+    <t>Window Functions</t>
+  </si>
+  <si>
+    <t>Stored Procedures</t>
+  </si>
+  <si>
+    <t>Indexes</t>
+  </si>
+  <si>
+    <t>Execution Plans</t>
+  </si>
+  <si>
+    <t>Query Optimization</t>
+  </si>
+  <si>
+    <t>Isolation Levels</t>
+  </si>
+  <si>
+    <t>Locks &amp; Deadlocks</t>
+  </si>
+  <si>
+    <t>SQL + EF Core</t>
+  </si>
+  <si>
+    <t>Views</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Temp Tables</t>
+  </si>
+  <si>
+    <t>Table Variables</t>
+  </si>
+  <si>
+    <t>Normalization</t>
+  </si>
+  <si>
+    <t>Partitioning</t>
+  </si>
+  <si>
+    <t>Caching</t>
+  </si>
+  <si>
+    <t>Connection Pooling</t>
+  </si>
+  <si>
+    <t>Query Store</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>🟢 Senior / System Design</t>
+  </si>
+  <si>
+    <t>Disaster Recovery</t>
+  </si>
+  <si>
+    <t>Multi-Tenant Database</t>
+  </si>
+  <si>
+    <t>Multi-Region Database</t>
+  </si>
+  <si>
+    <t>Best sequence for you:</t>
+  </si>
+  <si>
+    <t>SQL Basics → Joins → Subqueries → CTE → Functions → Stored Procedures → Window Functions → Indexing → Execution Plans → Optimization → Transactions → Concurrency → Locks/Deadlocks → SQL + EF Core → Scaling.</t>
+  </si>
+  <si>
+    <t>Bilkul bhai. Current LeetCode par SQL 50 official study plan basic → intermediate ke 50 questions deta hai, aur Advanced SQL 50 advanced level ke 50 questions deta hai. (LeetCode)</t>
+  </si>
+  <si>
+    <t>Tum 5+ years .NET + SQL Server interview prep kar rahe ho, isliye main sirf random order nahi dunga — Easy → Medium → Hard + topic progression mein karna better hai. LeetCode ke SQL problems mein joins, aggregation, subqueries, window functions aur CTEs progressively important hote hain. (LeetCode)</t>
+  </si>
+  <si>
+    <t>🟢 Phase 1 — SQL Easy Foundation</t>
+  </si>
+  <si>
+    <t>1. 175 — Combine Two Tables</t>
+  </si>
+  <si>
+    <t>2. 181 — Employees Earning More Than Their Managers</t>
+  </si>
+  <si>
+    <t>3. 182 — Duplicate Emails</t>
+  </si>
+  <si>
+    <t>4. 183 — Customers Who Never Order</t>
+  </si>
+  <si>
+    <t>5. 196 — Delete Duplicate Emails</t>
+  </si>
+  <si>
+    <t>6. 197 — Rising Temperature</t>
+  </si>
+  <si>
+    <t>7. 511 — Game Play Analysis I</t>
+  </si>
+  <si>
+    <t>8. 577 — Employee Bonus</t>
+  </si>
+  <si>
+    <t>9. 584 — Find Customer Referee</t>
+  </si>
+  <si>
+    <t>10. 586 — Customer Placing the Largest Number of Orders</t>
+  </si>
+  <si>
+    <t>11. 595 — Big Countries</t>
+  </si>
+  <si>
+    <t>12. 596 — Classes More Than 5 Students</t>
+  </si>
+  <si>
+    <t>13. 597 — Friend Requests I: Overall Acceptance Rate</t>
+  </si>
+  <si>
+    <t>14. 603 — Consecutive Available Seats</t>
+  </si>
+  <si>
+    <t>15. 607 — Sales Person</t>
+  </si>
+  <si>
+    <t>16. 610 — Triangle Judgement</t>
+  </si>
+  <si>
+    <t>17. 619 — Biggest Single Number</t>
+  </si>
+  <si>
+    <t>18. 620 — Not Boring Movies</t>
+  </si>
+  <si>
+    <t>19. 627 — Swap Salary</t>
+  </si>
+  <si>
+    <t>20. 1050 — Actors and Directors Who Cooperated At Least Three Times</t>
+  </si>
+  <si>
+    <t>21. 1068 — Product Sales Analysis I</t>
+  </si>
+  <si>
+    <t>22. 1075 — Project Employees I</t>
+  </si>
+  <si>
+    <t>23. 1084 — Sales Analysis III</t>
+  </si>
+  <si>
+    <t>24. 1141 — User Activity for the Past 30 Days I</t>
+  </si>
+  <si>
+    <t>25. 1148 — Article Views I</t>
+  </si>
+  <si>
+    <t>26. 1179 — Reformat Department Table</t>
+  </si>
+  <si>
+    <t>27. 1280 — Students and Examinations</t>
+  </si>
+  <si>
+    <t>28. 1294 — Weather Type in Each Country</t>
+  </si>
+  <si>
+    <t>29. 1378 — Replace Employee ID With The Unique Identifier</t>
+  </si>
+  <si>
+    <t>30. 1484 — Group Sold Products By The Date</t>
+  </si>
+  <si>
+    <t>31. 1517 — Find Users With Valid E-Mails</t>
+  </si>
+  <si>
+    <t>32. 1527 — Patients With a Condition</t>
+  </si>
+  <si>
+    <t>33. 1581 — Customer Who Visited but Did Not Make Any Transactions</t>
+  </si>
+  <si>
+    <t>34. 1587 — Bank Account Summary II</t>
+  </si>
+  <si>
+    <t>35. 1661 — Average Time of Process per Machine</t>
+  </si>
+  <si>
+    <t>36. 1729 — Find Followers Count</t>
+  </si>
+  <si>
+    <t>37. 1731 — The Number of Employees Which Report to Each Employee</t>
+  </si>
+  <si>
+    <t>38. 1741 — Find Total Time Spent by Each Employee</t>
+  </si>
+  <si>
+    <t>39. 1795 — Rearrange Products Table</t>
+  </si>
+  <si>
+    <t>40. 1873 — Calculate Special Bonus</t>
+  </si>
+  <si>
+    <t>41. 1907 — Count Salary Categories</t>
+  </si>
+  <si>
+    <t>42. 1965 — Employees With Missing Information</t>
+  </si>
+  <si>
+    <t>43. 1978 — Employees Whose Manager Left the Company</t>
+  </si>
+  <si>
+    <t>44. 2356 — Number of Unique Subjects Taught by Each Teacher</t>
+  </si>
+  <si>
+    <t>45. 3436 — Find Valid Emails</t>
+  </si>
+  <si>
+    <t>🟡 Phase 2 — Medium: JOIN + GROUP BY + Subquery</t>
+  </si>
+  <si>
+    <t>46. 176 — Second Highest Salary</t>
+  </si>
+  <si>
+    <t>47. 177 — Nth Highest Salary</t>
+  </si>
+  <si>
+    <t>48. 178 — Rank Scores</t>
+  </si>
+  <si>
+    <t>49. 180 — Consecutive Numbers</t>
+  </si>
+  <si>
+    <t>50. 184 — Department Highest Salary</t>
+  </si>
+  <si>
+    <t>51. 185 — Department Top Three Salaries</t>
+  </si>
+  <si>
+    <t>52. 570 — Managers with at Least 5 Direct Reports</t>
+  </si>
+  <si>
+    <t>53. 574 — Winning Candidate</t>
+  </si>
+  <si>
+    <t>54. 578 — Get Highest Answer Rate Question</t>
+  </si>
+  <si>
+    <t>55. 580 — Count Student Number in Departments</t>
+  </si>
+  <si>
+    <t>56. 585 — Investments in 2016</t>
+  </si>
+  <si>
+    <t>57. 608 — Tree Node</t>
+  </si>
+  <si>
+    <t>58. 612 — Shortest Distance in a Plane</t>
+  </si>
+  <si>
+    <t>59. 613 — Shortest Distance in a Line</t>
+  </si>
+  <si>
+    <t>60. 614 — Second Degree Follower</t>
+  </si>
+  <si>
+    <t>61. 626 — Exchange Seats</t>
+  </si>
+  <si>
+    <t>62. 1045 — Customers Who Bought All Products</t>
+  </si>
+  <si>
+    <t>63. 1070 — Product Sales Analysis III</t>
+  </si>
+  <si>
+    <t>64. 1076 — Project Employees II</t>
+  </si>
+  <si>
+    <t>65. 1077 — Project Employees III</t>
+  </si>
+  <si>
+    <t>66. 1083 — Sales Analysis II</t>
+  </si>
+  <si>
+    <t>67. 1098 — Unpopular Books</t>
+  </si>
+  <si>
+    <t>68. 1107 — New Users Daily Count</t>
+  </si>
+  <si>
+    <t>69. 1112 — Highest Grade For Each Student</t>
+  </si>
+  <si>
+    <t>70. 1126 — Active Businesses</t>
+  </si>
+  <si>
+    <t>71. 1132 — Reported Posts II</t>
+  </si>
+  <si>
+    <t>72. 1142 — User Activity for the Past 30 Days II</t>
+  </si>
+  <si>
+    <t>73. 1158 — Market Analysis I</t>
+  </si>
+  <si>
+    <t>74. 1164 — Product Price at a Given Date</t>
+  </si>
+  <si>
+    <t>75. 1174 — Immediate Food Delivery II</t>
+  </si>
+  <si>
+    <t>76. 1204 — Last Person to Fit in the Bus</t>
+  </si>
+  <si>
+    <t>77. 1205 — Monthly Transactions II</t>
+  </si>
+  <si>
+    <t>78. 1211 — Queries Quality and Percentage</t>
+  </si>
+  <si>
+    <t>79. 1251 — Average Selling Price</t>
+  </si>
+  <si>
+    <t>80. 1285 — Find the Start and End Number of Continuous Ranges</t>
+  </si>
+  <si>
+    <t>81. 1321 — Restaurant Growth</t>
+  </si>
+  <si>
+    <t>82. 1341 — Movie Rating</t>
+  </si>
+  <si>
+    <t>83. 1350 — Students With Invalid Departments</t>
+  </si>
+  <si>
+    <t>84. 1393 — Capital Gain/Loss</t>
+  </si>
+  <si>
+    <t>85. 1440 — Evaluate Boolean Expression</t>
+  </si>
+  <si>
+    <t>86. 1445 — Apples &amp; Oranges</t>
+  </si>
+  <si>
+    <t>87. 1454 — Active Users</t>
+  </si>
+  <si>
+    <t>88. 1495 — Friendly Movies Streamed Last Month</t>
+  </si>
+  <si>
+    <t>89. 1501 — Countries You Can Safely Invest In</t>
+  </si>
+  <si>
+    <t>90. 1532 — The Most Recent Three Orders</t>
+  </si>
+  <si>
+    <t>91. 1543 — Fix Product Name Format</t>
+  </si>
+  <si>
+    <t>92. 1596 — The Most Frequently Ordered Products for Each Customer</t>
+  </si>
+  <si>
+    <t>93. 1635 — Hopper Company Queries I</t>
+  </si>
+  <si>
+    <t>94. 1693 — Daily Leads and Partners</t>
+  </si>
+  <si>
+    <t>95. 1699 — Number of Calls Between Two Persons</t>
+  </si>
+  <si>
+    <t>96. 1709 — Biggest Window Between Visits</t>
+  </si>
+  <si>
+    <t>97. 1735 — Count Ways to Build Rooms in an Ant Colony</t>
+  </si>
+  <si>
+    <t>98. 1747 — Leetflex Banned Accounts</t>
+  </si>
+  <si>
+    <t>99. 1783 — Grand Slam Titles</t>
+  </si>
+  <si>
+    <t>100. 1789 — Primary Department for Each Employee</t>
+  </si>
+  <si>
+    <t>🟠 Phase 3 — Medium Advanced</t>
+  </si>
+  <si>
+    <t>101. 1809 — Ad-Free Sessions</t>
+  </si>
+  <si>
+    <t>102. 1821 — Find Customers With Positive Revenue This Year</t>
+  </si>
+  <si>
+    <t>103. 1841 — League Statistics</t>
+  </si>
+  <si>
+    <t>104. 1853 — Convert Date Format</t>
+  </si>
+  <si>
+    <t>105. 1867 — Orders With Maximum Quantity Above Average</t>
+  </si>
+  <si>
+    <t>106. 1890 — The Latest Login in 2020</t>
+  </si>
+  <si>
+    <t>107. 1900 — The Earliest and Latest Rounds Where Players Compete</t>
+  </si>
+  <si>
+    <t>108. 1934 — Confirmation Rate</t>
+  </si>
+  <si>
+    <t>109. 1949 — Strong Friendship</t>
+  </si>
+  <si>
+    <t>110. 1951 — All the Pairs With the Maximum Number of Common Followers</t>
+  </si>
+  <si>
+    <t>111. 1958 — Check if Move is Legal</t>
+  </si>
+  <si>
+    <t>112. 1961 — Check If String Is a Prefix of Array</t>
+  </si>
+  <si>
+    <t>113. 1972 — First and Last Call On the Same Day</t>
+  </si>
+  <si>
+    <t>114. 1988 — Find Cutoff Score for Each School</t>
+  </si>
+  <si>
+    <t>115. 1990 — Count the Number of Experiments</t>
+  </si>
+  <si>
+    <t>116. 2020 — Number of Accounts That Did Not Stream</t>
+  </si>
+  <si>
+    <t>117. 2024 — Maximize the Confusion of an Exam</t>
+  </si>
+  <si>
+    <t>118. 2051 — The Category of Each Member in the Store</t>
+  </si>
+  <si>
+    <t>119. 2112 — The Airport With the Most Traffic</t>
+  </si>
+  <si>
+    <t>120. 2142 — The Number of Passengers in Each Bus I</t>
+  </si>
+  <si>
+    <t>121. 2153 — The Number of Passengers in Each Bus II</t>
+  </si>
+  <si>
+    <t>122. 2173 — Longest Winning Streak</t>
+  </si>
+  <si>
+    <t>123. 2199 — Finding the Topic of Each Post</t>
+  </si>
+  <si>
+    <t>124. 2228 — Users With Two Purchases Within Seven Days</t>
+  </si>
+  <si>
+    <t>125. 2252 — Dynamic Pivoting of a Table</t>
+  </si>
+  <si>
+    <t>126. 2292 — Products With Three or More Orders in Two Consecutive Years</t>
+  </si>
+  <si>
+    <t>127. 2298 — Tasks Count in the Weekend</t>
+  </si>
+  <si>
+    <t>128. 2324 — Product Sales Analysis IV</t>
+  </si>
+  <si>
+    <t>129. 2329 — Product Sales Analysis V</t>
+  </si>
+  <si>
+    <t>130. 2346 — Compute the Rank as a Percentage</t>
+  </si>
+  <si>
+    <t>131. 2372 — Calculate the Influence of Each Salesperson</t>
+  </si>
+  <si>
+    <t>132. 2377 — Sort the Olympic Table</t>
+  </si>
+  <si>
+    <t>133. 2388 — Change Null Values in a Table to the Previous Value</t>
+  </si>
+  <si>
+    <t>134. 2394 — Employees With Deductions</t>
+  </si>
+  <si>
+    <t>135. 2404 — Most Frequent Even Element</t>
+  </si>
+  <si>
+    <t>136. 2412 — Minimum Money Required Before Transactions</t>
+  </si>
+  <si>
+    <t>137. 2474 — Customers With Strictly Increasing Purchases</t>
+  </si>
+  <si>
+    <t>138. 2480 — Form a Chemical Bond</t>
+  </si>
+  <si>
+    <t>139. 2486 — Append Characters to String to Make Subsequence</t>
+  </si>
+  <si>
+    <t>140. 2504 — Concatenate the Names</t>
+  </si>
+  <si>
+    <t>141. 2668 — Find Latest Salaries</t>
+  </si>
+  <si>
+    <t>142. 2669 — Count Artist Occurrences On Spotify Ranking List</t>
+  </si>
+  <si>
+    <t>143. 2686 — Immediate Food Delivery III</t>
+  </si>
+  <si>
+    <t>144. 2720 — Popularity Percentage</t>
+  </si>
+  <si>
+    <t>145. 2736 — Maximum Sum Queries</t>
+  </si>
+  <si>
+    <t>146. 2793 — Status of Flight Tickets</t>
+  </si>
+  <si>
+    <t>147. 2984 — Find Peak Calling Days</t>
+  </si>
+  <si>
+    <t>148. 2985 — Calculate Compressed Mean</t>
+  </si>
+  <si>
+    <t>149. 2986 — Find Third Transaction</t>
+  </si>
+  <si>
+    <t>150. 2990 — Loan Types</t>
+  </si>
+  <si>
+    <t>🔴 Phase 4 — Hard SQL</t>
+  </si>
+  <si>
+    <t>151. 262 — Trips and Users</t>
+  </si>
+  <si>
+    <t>152. 569 — Median Employee Salary</t>
+  </si>
+  <si>
+    <t>153. 571 — Find Median Given Frequency of Numbers</t>
+  </si>
+  <si>
+    <t>154. 579 — Find Cumulative Salary of an Employee</t>
+  </si>
+  <si>
+    <t>155. 601 — Human Traffic of Stadium</t>
+  </si>
+  <si>
+    <t>156. 615 — Average Salary: Departments VS Company</t>
+  </si>
+  <si>
+    <t>157. 618 — Students Report By Geography</t>
+  </si>
+  <si>
+    <t>158. 1097 — Game Play Analysis V</t>
+  </si>
+  <si>
+    <t>159. 1127 — User Purchase Platform</t>
+  </si>
+  <si>
+    <t>160. 1159 — Market Analysis II</t>
+  </si>
+  <si>
+    <t>161. 1194 — Tournament Winners</t>
+  </si>
+  <si>
+    <t>162. 1225 — Report Contiguous Dates</t>
+  </si>
+  <si>
+    <t>163. 1336 — Number of Transactions per Visit</t>
+  </si>
+  <si>
+    <t>164. 1369 — Get the Second Most Recent Activity</t>
+  </si>
+  <si>
+    <t>165. 1412 — Find the Quiet Students in All Exams</t>
+  </si>
+  <si>
+    <t>166. 1479 — Sales by Day of the Week</t>
+  </si>
+  <si>
+    <t>167. 1511 — Customer Order Frequency</t>
+  </si>
+  <si>
+    <t>168. 1537 — Get the Second Most Recent Activity</t>
+  </si>
+  <si>
+    <t>169. 1549 — The Most Recent Orders for Each Product</t>
+  </si>
+  <si>
+    <t>170. 1597 — Build Binary Expression Tree From Infix Expression</t>
+  </si>
+  <si>
+    <t>171. 1613 — Find the Missing IDs</t>
+  </si>
+  <si>
+    <t>172. 1635 — Hopper Company Queries I</t>
+  </si>
+  <si>
+    <t>173. 1636 — Sort Array by Increasing Frequency</t>
+  </si>
+  <si>
+    <t>174. 1645 — Hopper Company Queries II</t>
+  </si>
+  <si>
+    <t>175. 1651 — Hopper Company Queries III</t>
+  </si>
+  <si>
+    <t>176. 1667 — Fix Names in a Table</t>
+  </si>
+  <si>
+    <t>177. 1709 — Biggest Window Between Visits</t>
+  </si>
+  <si>
+    <t>178. 1715 — Count Apples and Oranges</t>
+  </si>
+  <si>
+    <t>179. 1747 — Leetflex Banned Accounts</t>
+  </si>
+  <si>
+    <t>180. 1767 — Find the Subtasks That Did Not Execute</t>
+  </si>
+  <si>
+    <t>181. 1783 — Grand Slam Titles</t>
+  </si>
+  <si>
+    <t>182. 1843 — Suspicious Bank Accounts</t>
+  </si>
+  <si>
+    <t>183. 185 — Department Top Three Salaries</t>
+  </si>
+  <si>
+    <t>184. 579 — Find Cumulative Salary of an Employee</t>
+  </si>
+  <si>
+    <t>185. 601 — Human Traffic of Stadium</t>
+  </si>
+  <si>
+    <t>🔥 But tumhare liye ek important point</t>
+  </si>
+  <si>
+    <t>151+ questions blindly karne ki zarurat nahi hai.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tumhare </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5+ years .NET + SQL Server</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> profile ke liye main preparation ko is tarah divide karunga:</t>
+    </r>
+  </si>
+  <si>
+    <t>Level 1 — Must Do</t>
+  </si>
+  <si>
+    <t>1–45</t>
+  </si>
+  <si>
+    <t>Isse SQL fundamentals strong honge.</t>
+  </si>
+  <si>
+    <t>Level 2 — Interview Core</t>
+  </si>
+  <si>
+    <t>46–100</t>
+  </si>
+  <si>
+    <t>Yahan:</t>
+  </si>
+  <si>
+    <t>JOIN</t>
+  </si>
+  <si>
+    <t>Subquery</t>
+  </si>
+  <si>
+    <t>CASE</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>Aggregation</t>
+  </si>
+  <si>
+    <t>strong honge.</t>
+  </si>
+  <si>
+    <t>Level 3 — Senior SQL</t>
+  </si>
+  <si>
+    <t>101–150</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>LAG/LEAD</t>
+  </si>
+  <si>
+    <t>Complex JOIN</t>
+  </si>
+  <si>
+    <t>Date problems</t>
+  </si>
+  <si>
+    <t>Advanced aggregation</t>
+  </si>
+  <si>
+    <t>aayega.</t>
+  </si>
+  <si>
+    <t>Level 4 — Hard</t>
+  </si>
+  <si>
+    <t>151–185</t>
+  </si>
+  <si>
+    <t>Ye tab karo jab upar ke concepts comfortable ho jayein.</t>
+  </si>
+  <si>
+    <t>⭐ Specially mark these</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Interview ke liye in concepts ko </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>red priority</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do:</t>
+    </r>
+  </si>
+  <si>
+    <t>176  Second Highest Salary</t>
+  </si>
+  <si>
+    <t>177  Nth Highest Salary</t>
+  </si>
+  <si>
+    <t>178  Rank Scores</t>
+  </si>
+  <si>
+    <t>180  Consecutive Numbers</t>
+  </si>
+  <si>
+    <t>184  Department Highest Salary</t>
+  </si>
+  <si>
+    <t>185  Department Top Three Salaries</t>
+  </si>
+  <si>
+    <t>601  Human Traffic of Stadium</t>
+  </si>
+  <si>
+    <t>1070 Product Sales Analysis</t>
+  </si>
+  <si>
+    <t>1112 Highest Grade For Each Student</t>
+  </si>
+  <si>
+    <t>1164 Product Price at a Given Date</t>
+  </si>
+  <si>
+    <t>1204 Last Person to Fit in the Bus</t>
+  </si>
+  <si>
+    <t>1321 Restaurant Growth</t>
+  </si>
+  <si>
+    <t>1454 Active Users</t>
+  </si>
+  <si>
+    <t>1532 Most Recent Three Orders</t>
+  </si>
+  <si>
+    <t>1544/1543 Product Name problems</t>
+  </si>
+  <si>
+    <t>1596 Most Frequently Ordered Products</t>
+  </si>
+  <si>
+    <t>1699 Number of Calls</t>
+  </si>
+  <si>
+    <t>1853 Convert Date Format</t>
+  </si>
+  <si>
+    <t>Ek correction: upar wali list ko “current LeetCode ke literally all SQL problems” mat samajhna—LeetCode ka database catalog dynamic hai, aur official SQL 50 + Advanced SQL 50 separate study plans hain. (LeetCode)</t>
+  </si>
+  <si>
+    <t>Agar target 5+ years .NET interview hai, to SQL 50 → Advanced SQL 50 complete karna sabse clean path hai. (LeetCode)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7471,6 +9677,14 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -7702,7 +9916,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -7854,7 +10068,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9998,6 +12224,669 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638825F5-223F-4189-9563-B7916650E823}">
+  <dimension ref="A2:A167"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="28" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="28" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="28" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="28" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="28" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="28" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="28" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="28" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="28" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="28" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="28" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="28" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="28" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="28" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="28" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="28" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="28" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="28" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="28" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="28" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="28" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="28" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="28" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CA00FF-4BF8-4980-95A2-47DC93F2BF72}">
   <dimension ref="B1:C942"/>
@@ -10022,7 +12911,7 @@
       <c r="B4" s="63" t="s">
         <v>1284</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="77" t="s">
         <v>139</v>
       </c>
     </row>
@@ -21279,6 +24168,4421 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E71FFFC-02B8-4BF3-B596-CA2AF57CFFD1}">
+  <dimension ref="B1:D844"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="88.140625" customWidth="1"/>
+    <col min="4" max="4" width="101.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4">
+      <c r="D1" s="79" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" ht="31.5">
+      <c r="B2" s="65" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B3" s="1"/>
+      <c r="D3" s="80" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="24.75" thickBot="1">
+      <c r="B4" s="63" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="2:4" ht="24">
+      <c r="B5" s="56"/>
+      <c r="D5" s="76" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="56" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D6" s="56"/>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="56"/>
+      <c r="D7" s="56" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="56" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D8" s="56"/>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="56"/>
+      <c r="D9" s="56" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="56" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D10" s="56"/>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="56"/>
+      <c r="D11" s="56" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="56" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D12" s="56"/>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="56"/>
+      <c r="D13" s="56" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="56" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D14" s="56"/>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="56"/>
+      <c r="D15" s="56" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="56" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D16" s="56"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="56"/>
+      <c r="D17" s="56" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="56" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D18" s="56"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="56"/>
+      <c r="D19" s="56" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="56" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D20" s="56"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="56"/>
+      <c r="D21" s="56" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="56" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D22" s="56"/>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="56"/>
+      <c r="D23" s="56" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="56" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D24" s="56"/>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="56"/>
+      <c r="D25" s="56" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="57" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D26" s="56"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="56"/>
+      <c r="D27" s="56" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="57" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D28" s="56"/>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="56"/>
+      <c r="D29" s="56" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="57" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D30" s="56"/>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="56"/>
+      <c r="D31" s="56" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="57" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D32" s="56"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="56"/>
+      <c r="D33" s="56" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="57" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D34" s="56"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="56"/>
+      <c r="D35" s="56" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="57" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D36" s="56"/>
+    </row>
+    <row r="37" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B37" s="1"/>
+      <c r="D37" s="56" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B38" s="59" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D38" s="56"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="56"/>
+      <c r="D39" s="56" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="56" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D40" s="56"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="56"/>
+      <c r="D41" s="56" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="56" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D42" s="56"/>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="56"/>
+      <c r="D43" s="56" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="56" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D44" s="56"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="56"/>
+      <c r="D45" s="56" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="56" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D46" s="56"/>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="56"/>
+      <c r="D47" s="56" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="56" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D48" s="56"/>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="56"/>
+      <c r="D49" s="56" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="56" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D50" s="56"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="56"/>
+      <c r="D51" s="56" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="56" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D52" s="56"/>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="56"/>
+      <c r="D53" s="56" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="56" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D54" s="56"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="56"/>
+      <c r="D55" s="56" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="56" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D56" s="56"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="56"/>
+      <c r="D57" s="56" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="56" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D58" s="56"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="56"/>
+      <c r="D59" s="56" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="56" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D60" s="56"/>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="56"/>
+      <c r="D61" s="56" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="56" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D62" s="56"/>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="56"/>
+      <c r="D63" s="56" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="56" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D64" s="56"/>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="56"/>
+      <c r="D65" s="56" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="56" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D66" s="56"/>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="56"/>
+      <c r="D67" s="56" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="56" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D68" s="56"/>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="56"/>
+      <c r="D69" s="56" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="56" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D70" s="56"/>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="56"/>
+      <c r="D71" s="56" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="56" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D72" s="56"/>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="56"/>
+      <c r="D73" s="56" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="56" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D74" s="56"/>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="56"/>
+      <c r="D75" s="56" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="56" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D76" s="56"/>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" s="56"/>
+      <c r="D77" s="56" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="56" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D78" s="56"/>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" s="1"/>
+      <c r="D79" s="56" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="18">
+      <c r="B80" s="78" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D80" s="56"/>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="56"/>
+      <c r="D81" s="56" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="57" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D82" s="56"/>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" s="56"/>
+      <c r="D83" s="56" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="57" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D84" s="56"/>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" s="56"/>
+      <c r="D85" s="56" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" s="57" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D86" s="56"/>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" s="56"/>
+      <c r="D87" s="56" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" s="57" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D88" s="56"/>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="56"/>
+      <c r="D89" s="56" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="57" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D90" s="56"/>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="1"/>
+      <c r="D91" s="56" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" ht="31.5">
+      <c r="B92" s="65" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D92" s="56"/>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="56"/>
+      <c r="D93" s="56" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="57" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D94" s="56"/>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="56"/>
+      <c r="D95" s="56" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="57" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D96" s="1"/>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="56"/>
+      <c r="D97" s="1"/>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="57" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D98" s="1"/>
+    </row>
+    <row r="99" spans="2:4" ht="31.5">
+      <c r="B99" s="56"/>
+      <c r="D99" s="75" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="57" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D100" s="56"/>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="56"/>
+      <c r="D101" s="56" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="57" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D102" s="56"/>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="56"/>
+      <c r="D103" s="56" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="57" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D104" s="56"/>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="56"/>
+      <c r="D105" s="56" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="57" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D106" s="56"/>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="56"/>
+      <c r="D107" s="56" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="57" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D108" s="56"/>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="56"/>
+      <c r="D109" s="56" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="56" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D110" s="56"/>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="56"/>
+      <c r="D111" s="56" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="56" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D112" s="56"/>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" s="56"/>
+      <c r="D113" s="56" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="57" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D114" s="56"/>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="56"/>
+      <c r="D115" s="56" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="57" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D116" s="56"/>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="56"/>
+      <c r="D117" s="56" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="57" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D118" s="56"/>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="56"/>
+      <c r="D119" s="56" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="57" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D120" s="56"/>
+    </row>
+    <row r="121" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B121" s="1"/>
+      <c r="D121" s="56" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B122" s="59" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D122" s="56"/>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" s="56"/>
+      <c r="D123" s="56" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" s="56" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D124" s="56"/>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="56"/>
+      <c r="D125" s="56" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="56" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D126" s="56"/>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="56"/>
+      <c r="D127" s="56" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="56" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D128" s="56"/>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="56"/>
+      <c r="D129" s="56" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="57" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D130" s="56"/>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="56"/>
+      <c r="D131" s="56" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="57" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D132" s="56"/>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="56"/>
+      <c r="D133" s="56" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" s="57" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D134" s="56"/>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="56"/>
+      <c r="D135" s="56" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="57" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D136" s="56"/>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="56"/>
+      <c r="D137" s="56" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="57" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D138" s="56"/>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="56"/>
+      <c r="D139" s="56" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="57" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D140" s="56"/>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" s="56"/>
+      <c r="D141" s="56" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="57" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D142" s="56"/>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="56"/>
+      <c r="D143" s="56" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="56" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D144" s="56"/>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="56"/>
+      <c r="D145" s="56" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="57" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D146" s="56"/>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="56"/>
+      <c r="D147" s="56" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="57" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D148" s="56"/>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="56"/>
+      <c r="D149" s="56" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="57" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D150" s="56"/>
+    </row>
+    <row r="151" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B151" s="1"/>
+      <c r="D151" s="56" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B152" s="59" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D152" s="56"/>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="56"/>
+      <c r="D153" s="56" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="57" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D154" s="56"/>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="56"/>
+      <c r="D155" s="56" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="57" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D156" s="56"/>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="56"/>
+      <c r="D157" s="56" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="57" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D158" s="56"/>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="56"/>
+      <c r="D159" s="56" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="57" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D160" s="56"/>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="56"/>
+      <c r="D161" s="56" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="57" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D162" s="56"/>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="1"/>
+      <c r="D163" s="56" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" ht="18">
+      <c r="B164" s="55" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D164" s="56"/>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="1"/>
+      <c r="D165" s="56" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="66" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D166" s="56"/>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="66" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D167" s="56" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" s="66" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D168" s="56"/>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="1"/>
+      <c r="D169" s="56" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D170" s="56"/>
+    </row>
+    <row r="171" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B171" s="1"/>
+      <c r="D171" s="56" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B172" s="59" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D172" s="56"/>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="1"/>
+      <c r="D173" s="56" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" ht="18">
+      <c r="B174" s="55" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D174" s="56"/>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="56"/>
+      <c r="D175" s="56" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" s="57" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D176" s="56"/>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" s="56"/>
+      <c r="D177" s="56" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" s="57" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D178" s="56"/>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="56"/>
+      <c r="D179" s="56" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" s="57" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D180" s="56"/>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" s="56"/>
+      <c r="D181" s="56" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" s="57" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D182" s="56"/>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="56"/>
+      <c r="D183" s="56" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="57" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D184" s="56"/>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="56"/>
+      <c r="D185" s="56" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="57" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D186" s="56"/>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" s="56"/>
+      <c r="D187" s="56" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="57" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D188" s="56"/>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" s="56"/>
+      <c r="D189" s="56" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="57" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D190" s="56"/>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" s="56"/>
+      <c r="D191" s="56" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="57" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D192" s="56"/>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="56"/>
+      <c r="D193" s="56" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" s="57" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D194" s="56"/>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="B195" s="1"/>
+      <c r="D195" s="56" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4" ht="18">
+      <c r="B196" s="55" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D196" s="56"/>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" s="56"/>
+      <c r="D197" s="56" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="B198" s="57" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D198" s="56"/>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199" s="56"/>
+      <c r="D199" s="56" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" s="57" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D200" s="56"/>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="B201" s="56"/>
+      <c r="D201" s="56" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="57" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D202" s="56"/>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" s="56"/>
+      <c r="D203" s="56" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="B204" s="57" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D204" s="56"/>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205" s="56"/>
+      <c r="D205" s="56" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="B206" s="57" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D206" s="56"/>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" s="56"/>
+      <c r="D207" s="56" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208" s="57" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D208" s="56"/>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" s="56"/>
+      <c r="D209" s="56" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210" s="57" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D210" s="1"/>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" s="1"/>
+      <c r="D211" s="1"/>
+    </row>
+    <row r="212" spans="2:4" ht="18">
+      <c r="B212" s="55" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D212" s="1"/>
+    </row>
+    <row r="213" spans="2:4" ht="31.5">
+      <c r="B213" s="56"/>
+      <c r="D213" s="75" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="B214" s="57" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D214" s="56"/>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" s="56"/>
+      <c r="D215" s="56" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216" s="57" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D216" s="56"/>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="B217" s="56"/>
+      <c r="D217" s="56" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" s="57" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D218" s="56"/>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="B219" s="56"/>
+      <c r="D219" s="56" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220" s="57" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D220" s="56"/>
+    </row>
+    <row r="221" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B221" s="1"/>
+      <c r="D221" s="56" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B222" s="59" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D222" s="56"/>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="B223" s="56"/>
+      <c r="D223" s="56" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="57" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D224" s="56"/>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" s="56"/>
+      <c r="D225" s="56" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" s="57" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D226" s="56"/>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" s="56"/>
+      <c r="D227" s="56" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" s="57" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D228" s="56"/>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" s="56"/>
+      <c r="D229" s="56" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" s="57" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D230" s="56"/>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" s="56"/>
+      <c r="D231" s="56" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" s="57" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D232" s="56"/>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" s="1"/>
+      <c r="D233" s="56" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D234" s="56"/>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" s="56"/>
+      <c r="D235" s="56" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" s="57" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D236" s="56"/>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" s="56"/>
+      <c r="D237" s="56" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" s="57" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D238" s="56"/>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" s="1"/>
+      <c r="D239" s="56" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" ht="18">
+      <c r="B240" s="55" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D240" s="56"/>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" s="1"/>
+      <c r="D241" s="56" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242" s="66" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D242" s="56"/>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="B243" s="66" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D243" s="56" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4">
+      <c r="B244" s="66" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D244" s="56"/>
+    </row>
+    <row r="245" spans="2:4">
+      <c r="B245" s="66" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D245" s="56" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4">
+      <c r="B246" s="66" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D246" s="56"/>
+    </row>
+    <row r="247" spans="2:4">
+      <c r="B247" s="1"/>
+      <c r="D247" s="56" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4">
+      <c r="B248" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D248" s="56"/>
+    </row>
+    <row r="249" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B249" s="1"/>
+      <c r="D249" s="56" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B250" s="59" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D250" s="56"/>
+    </row>
+    <row r="251" spans="2:4">
+      <c r="B251" s="1"/>
+      <c r="D251" s="56" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4">
+      <c r="B252" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D252" s="56"/>
+    </row>
+    <row r="253" spans="2:4">
+      <c r="B253" s="56"/>
+      <c r="D253" s="56" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4">
+      <c r="B254" s="56" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D254" s="56"/>
+    </row>
+    <row r="255" spans="2:4">
+      <c r="B255" s="56"/>
+      <c r="D255" s="56" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4">
+      <c r="B256" s="56" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D256" s="56"/>
+    </row>
+    <row r="257" spans="2:4">
+      <c r="B257" s="56"/>
+      <c r="D257" s="56" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4">
+      <c r="B258" s="56" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D258" s="56"/>
+    </row>
+    <row r="259" spans="2:4">
+      <c r="B259" s="56"/>
+      <c r="D259" s="56" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4">
+      <c r="B260" s="56" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D260" s="56"/>
+    </row>
+    <row r="261" spans="2:4">
+      <c r="B261" s="56"/>
+      <c r="D261" s="56" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4">
+      <c r="B262" s="56" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D262" s="56"/>
+    </row>
+    <row r="263" spans="2:4">
+      <c r="B263" s="56"/>
+      <c r="D263" s="56" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4">
+      <c r="B264" s="56" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D264" s="56"/>
+    </row>
+    <row r="265" spans="2:4">
+      <c r="B265" s="1"/>
+      <c r="D265" s="56" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4" ht="18">
+      <c r="B266" s="55" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D266" s="56"/>
+    </row>
+    <row r="267" spans="2:4">
+      <c r="B267" s="56"/>
+      <c r="D267" s="56" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4">
+      <c r="B268" s="56" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D268" s="56"/>
+    </row>
+    <row r="269" spans="2:4">
+      <c r="B269" s="56"/>
+      <c r="D269" s="56" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4">
+      <c r="B270" s="56" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D270" s="56"/>
+    </row>
+    <row r="271" spans="2:4">
+      <c r="B271" s="56"/>
+      <c r="D271" s="56" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4">
+      <c r="B272" s="56" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D272" s="56"/>
+    </row>
+    <row r="273" spans="2:4">
+      <c r="B273" s="56"/>
+      <c r="D273" s="56" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="274" spans="2:4">
+      <c r="B274" s="56" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D274" s="56"/>
+    </row>
+    <row r="275" spans="2:4">
+      <c r="B275" s="56"/>
+      <c r="D275" s="56" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="276" spans="2:4">
+      <c r="B276" s="56" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D276" s="56"/>
+    </row>
+    <row r="277" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B277" s="1"/>
+      <c r="D277" s="56" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="278" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B278" s="59" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D278" s="56"/>
+    </row>
+    <row r="279" spans="2:4">
+      <c r="B279" s="56"/>
+      <c r="D279" s="56" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4">
+      <c r="B280" s="56" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D280" s="56"/>
+    </row>
+    <row r="281" spans="2:4">
+      <c r="B281" s="56"/>
+      <c r="D281" s="56" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="282" spans="2:4">
+      <c r="B282" s="56" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D282" s="56"/>
+    </row>
+    <row r="283" spans="2:4">
+      <c r="B283" s="56"/>
+      <c r="D283" s="56" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="284" spans="2:4">
+      <c r="B284" s="56" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D284" s="56"/>
+    </row>
+    <row r="285" spans="2:4">
+      <c r="B285" s="56"/>
+      <c r="D285" s="56" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="286" spans="2:4">
+      <c r="B286" s="56" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D286" s="56"/>
+    </row>
+    <row r="287" spans="2:4">
+      <c r="B287" s="56"/>
+      <c r="D287" s="56" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="288" spans="2:4">
+      <c r="B288" s="56" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D288" s="56"/>
+    </row>
+    <row r="289" spans="2:4">
+      <c r="B289" s="56"/>
+      <c r="D289" s="56" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4">
+      <c r="B290" s="56" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D290" s="56"/>
+    </row>
+    <row r="291" spans="2:4">
+      <c r="B291" s="56"/>
+      <c r="D291" s="56" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4">
+      <c r="B292" s="57" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D292" s="56"/>
+    </row>
+    <row r="293" spans="2:4">
+      <c r="B293" s="56"/>
+      <c r="D293" s="56" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4">
+      <c r="B294" s="57" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D294" s="56"/>
+    </row>
+    <row r="295" spans="2:4">
+      <c r="B295" s="56"/>
+      <c r="D295" s="56" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4">
+      <c r="B296" s="56" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D296" s="56"/>
+    </row>
+    <row r="297" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B297" s="1"/>
+      <c r="D297" s="56" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B298" s="59" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D298" s="56"/>
+    </row>
+    <row r="299" spans="2:4">
+      <c r="B299" s="56"/>
+      <c r="D299" s="56" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4">
+      <c r="B300" s="57" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D300" s="56"/>
+    </row>
+    <row r="301" spans="2:4">
+      <c r="B301" s="56"/>
+      <c r="D301" s="56" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4">
+      <c r="B302" s="57" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D302" s="56"/>
+    </row>
+    <row r="303" spans="2:4">
+      <c r="B303" s="56"/>
+      <c r="D303" s="56" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4">
+      <c r="B304" s="57" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D304" s="56"/>
+    </row>
+    <row r="305" spans="2:4">
+      <c r="B305" s="56"/>
+      <c r="D305" s="56" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4">
+      <c r="B306" s="57" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D306" s="56"/>
+    </row>
+    <row r="307" spans="2:4">
+      <c r="B307" s="1"/>
+      <c r="D307" s="56" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4">
+      <c r="B308" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D308" s="56"/>
+    </row>
+    <row r="309" spans="2:4">
+      <c r="B309" s="1"/>
+      <c r="D309" s="56" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4">
+      <c r="B310" s="66" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D310" s="56"/>
+    </row>
+    <row r="311" spans="2:4">
+      <c r="B311" s="66" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D311" s="56" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4">
+      <c r="B312" s="66" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D312" s="56"/>
+    </row>
+    <row r="313" spans="2:4">
+      <c r="B313" s="1"/>
+      <c r="D313" s="56" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4">
+      <c r="B314" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D314" s="1"/>
+    </row>
+    <row r="315" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B315" s="1"/>
+      <c r="D315" s="1"/>
+    </row>
+    <row r="316" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B316" s="59" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D316" s="1"/>
+    </row>
+    <row r="317" spans="2:4" ht="31.5">
+      <c r="B317" s="56"/>
+      <c r="D317" s="75" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4">
+      <c r="B318" s="56" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D318" s="56"/>
+    </row>
+    <row r="319" spans="2:4">
+      <c r="B319" s="56"/>
+      <c r="D319" s="56" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4">
+      <c r="B320" s="56" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D320" s="56"/>
+    </row>
+    <row r="321" spans="2:4">
+      <c r="B321" s="56"/>
+      <c r="D321" s="56" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4">
+      <c r="B322" s="56" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D322" s="56"/>
+    </row>
+    <row r="323" spans="2:4">
+      <c r="B323" s="56"/>
+      <c r="D323" s="56" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4">
+      <c r="B324" s="56" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D324" s="56"/>
+    </row>
+    <row r="325" spans="2:4">
+      <c r="B325" s="56"/>
+      <c r="D325" s="56" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4">
+      <c r="B326" s="56" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D326" s="56"/>
+    </row>
+    <row r="327" spans="2:4">
+      <c r="B327" s="56"/>
+      <c r="D327" s="56" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4">
+      <c r="B328" s="56" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D328" s="56"/>
+    </row>
+    <row r="329" spans="2:4">
+      <c r="B329" s="56"/>
+      <c r="D329" s="56" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4">
+      <c r="B330" s="56" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D330" s="56"/>
+    </row>
+    <row r="331" spans="2:4">
+      <c r="B331" s="56"/>
+      <c r="D331" s="56" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="332" spans="2:4">
+      <c r="B332" s="56" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D332" s="56"/>
+    </row>
+    <row r="333" spans="2:4">
+      <c r="B333" s="56"/>
+      <c r="D333" s="56" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4">
+      <c r="B334" s="56" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D334" s="56"/>
+    </row>
+    <row r="335" spans="2:4">
+      <c r="B335" s="1"/>
+      <c r="D335" s="56" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" ht="31.5">
+      <c r="B336" s="65" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D336" s="56"/>
+    </row>
+    <row r="337" spans="2:4">
+      <c r="B337" s="56"/>
+      <c r="D337" s="56" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4">
+      <c r="B338" s="56" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D338" s="56"/>
+    </row>
+    <row r="339" spans="2:4">
+      <c r="B339" s="56"/>
+      <c r="D339" s="56" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4">
+      <c r="B340" s="56" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D340" s="56"/>
+    </row>
+    <row r="341" spans="2:4">
+      <c r="B341" s="56"/>
+      <c r="D341" s="56" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4">
+      <c r="B342" s="56" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D342" s="56"/>
+    </row>
+    <row r="343" spans="2:4">
+      <c r="B343" s="56"/>
+      <c r="D343" s="56" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4">
+      <c r="B344" s="56" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D344" s="56"/>
+    </row>
+    <row r="345" spans="2:4">
+      <c r="B345" s="56"/>
+      <c r="D345" s="56" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="346" spans="2:4">
+      <c r="B346" s="56" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D346" s="56"/>
+    </row>
+    <row r="347" spans="2:4">
+      <c r="B347" s="56"/>
+      <c r="D347" s="56" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="348" spans="2:4">
+      <c r="B348" s="56" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D348" s="56"/>
+    </row>
+    <row r="349" spans="2:4">
+      <c r="B349" s="56"/>
+      <c r="D349" s="56" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="350" spans="2:4">
+      <c r="B350" s="56" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D350" s="56"/>
+    </row>
+    <row r="351" spans="2:4">
+      <c r="B351" s="56"/>
+      <c r="D351" s="56" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="352" spans="2:4">
+      <c r="B352" s="56" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D352" s="56"/>
+    </row>
+    <row r="353" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B353" s="1"/>
+      <c r="D353" s="56" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="354" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B354" s="59" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D354" s="56"/>
+    </row>
+    <row r="355" spans="2:4">
+      <c r="B355" s="1"/>
+      <c r="D355" s="56" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="356" spans="2:4">
+      <c r="B356" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D356" s="56"/>
+    </row>
+    <row r="357" spans="2:4">
+      <c r="B357" s="56"/>
+      <c r="D357" s="56" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="358" spans="2:4">
+      <c r="B358" s="56" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D358" s="56"/>
+    </row>
+    <row r="359" spans="2:4">
+      <c r="B359" s="56"/>
+      <c r="D359" s="56" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="360" spans="2:4">
+      <c r="B360" s="56" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D360" s="56"/>
+    </row>
+    <row r="361" spans="2:4">
+      <c r="B361" s="56"/>
+      <c r="D361" s="56" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="362" spans="2:4">
+      <c r="B362" s="56" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D362" s="56"/>
+    </row>
+    <row r="363" spans="2:4">
+      <c r="B363" s="56"/>
+      <c r="D363" s="56" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="364" spans="2:4">
+      <c r="B364" s="56" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D364" s="56"/>
+    </row>
+    <row r="365" spans="2:4">
+      <c r="B365" s="56"/>
+      <c r="D365" s="56" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="366" spans="2:4">
+      <c r="B366" s="56" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D366" s="56"/>
+    </row>
+    <row r="367" spans="2:4">
+      <c r="B367" s="56"/>
+      <c r="D367" s="56" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="368" spans="2:4">
+      <c r="B368" s="56" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D368" s="56"/>
+    </row>
+    <row r="369" spans="2:4">
+      <c r="B369" s="56"/>
+      <c r="D369" s="56" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="370" spans="2:4">
+      <c r="B370" s="56" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D370" s="56"/>
+    </row>
+    <row r="371" spans="2:4">
+      <c r="B371" s="56"/>
+      <c r="D371" s="56" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="372" spans="2:4">
+      <c r="B372" s="56" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D372" s="56"/>
+    </row>
+    <row r="373" spans="2:4">
+      <c r="B373" s="56"/>
+      <c r="D373" s="56" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="374" spans="2:4">
+      <c r="B374" s="56" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D374" s="56"/>
+    </row>
+    <row r="375" spans="2:4">
+      <c r="B375" s="56"/>
+      <c r="D375" s="56" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="376" spans="2:4">
+      <c r="B376" s="57" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D376" s="56"/>
+    </row>
+    <row r="377" spans="2:4">
+      <c r="B377" s="56"/>
+      <c r="D377" s="56" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="378" spans="2:4">
+      <c r="B378" s="56" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D378" s="56"/>
+    </row>
+    <row r="379" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B379" s="1"/>
+      <c r="D379" s="56" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="380" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B380" s="59" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D380" s="56"/>
+    </row>
+    <row r="381" spans="2:4">
+      <c r="B381" s="56"/>
+      <c r="D381" s="56" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="382" spans="2:4">
+      <c r="B382" s="56" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D382" s="56"/>
+    </row>
+    <row r="383" spans="2:4">
+      <c r="B383" s="56"/>
+      <c r="D383" s="56" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="384" spans="2:4">
+      <c r="B384" s="56" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D384" s="56"/>
+    </row>
+    <row r="385" spans="2:4">
+      <c r="B385" s="56"/>
+      <c r="D385" s="56" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="386" spans="2:4">
+      <c r="B386" s="56" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D386" s="56"/>
+    </row>
+    <row r="387" spans="2:4">
+      <c r="B387" s="56"/>
+      <c r="D387" s="56" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="388" spans="2:4">
+      <c r="B388" s="56" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D388" s="1"/>
+    </row>
+    <row r="389" spans="2:4">
+      <c r="B389" s="56"/>
+      <c r="D389" s="1"/>
+    </row>
+    <row r="390" spans="2:4">
+      <c r="B390" s="56" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D390" s="1"/>
+    </row>
+    <row r="391" spans="2:4" ht="24">
+      <c r="B391" s="56"/>
+      <c r="D391" s="76" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="392" spans="2:4">
+      <c r="B392" s="56" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D392" s="1"/>
+    </row>
+    <row r="393" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B393" s="1"/>
+      <c r="D393" s="43" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="394" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B394" s="59" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D394" s="1"/>
+    </row>
+    <row r="395" spans="2:4">
+      <c r="B395" s="1"/>
+      <c r="D395" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="396" spans="2:4">
+      <c r="B396" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D396" s="1"/>
+    </row>
+    <row r="397" spans="2:4" ht="18">
+      <c r="B397" s="56"/>
+      <c r="D397" s="55" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="398" spans="2:4">
+      <c r="B398" s="56" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D398" s="1"/>
+    </row>
+    <row r="399" spans="2:4">
+      <c r="B399" s="56"/>
+      <c r="D399" s="43" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="400" spans="2:4">
+      <c r="B400" s="56" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D400" s="1"/>
+    </row>
+    <row r="401" spans="2:4">
+      <c r="B401" s="56"/>
+      <c r="D401" s="1" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="402" spans="2:4">
+      <c r="B402" s="56" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D402" s="1"/>
+    </row>
+    <row r="403" spans="2:4" ht="18">
+      <c r="B403" s="56"/>
+      <c r="D403" s="55" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="404" spans="2:4">
+      <c r="B404" s="56" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D404" s="1"/>
+    </row>
+    <row r="405" spans="2:4">
+      <c r="B405" s="56"/>
+      <c r="D405" s="43" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="406" spans="2:4">
+      <c r="B406" s="56" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D406" s="1"/>
+    </row>
+    <row r="407" spans="2:4">
+      <c r="B407" s="56"/>
+      <c r="D407" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="408" spans="2:4">
+      <c r="B408" s="56" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D408" s="56"/>
+    </row>
+    <row r="409" spans="2:4">
+      <c r="B409" s="56"/>
+      <c r="D409" s="56" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="410" spans="2:4">
+      <c r="B410" s="56" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D410" s="56"/>
+    </row>
+    <row r="411" spans="2:4">
+      <c r="B411" s="56"/>
+      <c r="D411" s="56" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="412" spans="2:4">
+      <c r="B412" s="56" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D412" s="56"/>
+    </row>
+    <row r="413" spans="2:4">
+      <c r="B413" s="56"/>
+      <c r="D413" s="56" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="414" spans="2:4">
+      <c r="B414" s="56" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D414" s="56"/>
+    </row>
+    <row r="415" spans="2:4">
+      <c r="B415" s="56"/>
+      <c r="D415" s="56" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="416" spans="2:4">
+      <c r="B416" s="56" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D416" s="56"/>
+    </row>
+    <row r="417" spans="2:4">
+      <c r="B417" s="56"/>
+      <c r="D417" s="56" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="418" spans="2:4">
+      <c r="B418" s="56" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D418" s="56"/>
+    </row>
+    <row r="419" spans="2:4">
+      <c r="B419" s="56"/>
+      <c r="D419" s="56" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="420" spans="2:4">
+      <c r="B420" s="56" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D420" s="56"/>
+    </row>
+    <row r="421" spans="2:4">
+      <c r="B421" s="56"/>
+      <c r="D421" s="56" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="422" spans="2:4">
+      <c r="B422" s="56" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D422" s="56"/>
+    </row>
+    <row r="423" spans="2:4">
+      <c r="B423" s="56"/>
+      <c r="D423" s="56" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="424" spans="2:4">
+      <c r="B424" s="56" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D424" s="1"/>
+    </row>
+    <row r="425" spans="2:4">
+      <c r="B425" s="56"/>
+      <c r="D425" s="1" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="426" spans="2:4">
+      <c r="B426" s="56" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D426" s="1"/>
+    </row>
+    <row r="427" spans="2:4" ht="18">
+      <c r="B427" s="56"/>
+      <c r="D427" s="55" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="428" spans="2:4">
+      <c r="B428" s="56" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D428" s="1"/>
+    </row>
+    <row r="429" spans="2:4">
+      <c r="B429" s="56"/>
+      <c r="D429" s="43" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="430" spans="2:4">
+      <c r="B430" s="56" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D430" s="1"/>
+    </row>
+    <row r="431" spans="2:4">
+      <c r="B431" s="56"/>
+      <c r="D431" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="432" spans="2:4">
+      <c r="B432" s="56" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D432" s="56"/>
+    </row>
+    <row r="433" spans="2:4">
+      <c r="B433" s="56"/>
+      <c r="D433" s="56" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="434" spans="2:4">
+      <c r="B434" s="56" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D434" s="56"/>
+    </row>
+    <row r="435" spans="2:4">
+      <c r="B435" s="1"/>
+      <c r="D435" s="56" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="436" spans="2:4">
+      <c r="B436" s="1"/>
+      <c r="D436" s="56"/>
+    </row>
+    <row r="437" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B437" s="1"/>
+      <c r="D437" s="56" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="438" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B438" s="59" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D438" s="56"/>
+    </row>
+    <row r="439" spans="2:4">
+      <c r="B439" s="1"/>
+      <c r="D439" s="56" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="440" spans="2:4">
+      <c r="B440" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D440" s="56"/>
+    </row>
+    <row r="441" spans="2:4">
+      <c r="B441" s="56"/>
+      <c r="D441" s="56" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="442" spans="2:4">
+      <c r="B442" s="56" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D442" s="56"/>
+    </row>
+    <row r="443" spans="2:4">
+      <c r="B443" s="56"/>
+      <c r="D443" s="56" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="444" spans="2:4">
+      <c r="B444" s="56" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D444" s="56"/>
+    </row>
+    <row r="445" spans="2:4">
+      <c r="B445" s="56"/>
+      <c r="D445" s="56" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="446" spans="2:4">
+      <c r="B446" s="56" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D446" s="56"/>
+    </row>
+    <row r="447" spans="2:4">
+      <c r="B447" s="56"/>
+      <c r="D447" s="56" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="448" spans="2:4">
+      <c r="B448" s="56" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D448" s="1"/>
+    </row>
+    <row r="449" spans="2:4">
+      <c r="B449" s="56"/>
+      <c r="D449" s="1" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="450" spans="2:4">
+      <c r="B450" s="56" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D450" s="1"/>
+    </row>
+    <row r="451" spans="2:4" ht="18">
+      <c r="B451" s="56"/>
+      <c r="D451" s="55" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="452" spans="2:4">
+      <c r="B452" s="56" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D452" s="1"/>
+    </row>
+    <row r="453" spans="2:4">
+      <c r="B453" s="56"/>
+      <c r="D453" s="43" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="454" spans="2:4">
+      <c r="B454" s="56" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D454" s="1"/>
+    </row>
+    <row r="455" spans="2:4">
+      <c r="B455" s="56"/>
+      <c r="D455" s="1" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="456" spans="2:4">
+      <c r="B456" s="56" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D456" s="1"/>
+    </row>
+    <row r="457" spans="2:4">
+      <c r="B457" s="56"/>
+      <c r="D457" s="1"/>
+    </row>
+    <row r="458" spans="2:4">
+      <c r="B458" s="56" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D458" s="1"/>
+    </row>
+    <row r="459" spans="2:4" ht="18">
+      <c r="B459" s="56"/>
+      <c r="D459" s="55" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="460" spans="2:4">
+      <c r="B460" s="56" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D460" s="1"/>
+    </row>
+    <row r="461" spans="2:4">
+      <c r="B461" s="56"/>
+      <c r="D461" s="1" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="462" spans="2:4">
+      <c r="B462" s="56" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D462" s="1"/>
+    </row>
+    <row r="463" spans="2:4">
+      <c r="B463" s="56"/>
+      <c r="D463" s="66" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="464" spans="2:4">
+      <c r="B464" s="56" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D464" s="66" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="465" spans="2:4">
+      <c r="B465" s="56"/>
+      <c r="D465" s="66" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="466" spans="2:4">
+      <c r="B466" s="56" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D466" s="66" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="467" spans="2:4">
+      <c r="B467" s="56"/>
+      <c r="D467" s="66" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="468" spans="2:4">
+      <c r="B468" s="56" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D468" s="66" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="469" spans="2:4">
+      <c r="B469" s="56"/>
+      <c r="D469" s="66" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="470" spans="2:4">
+      <c r="B470" s="56" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D470" s="66" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="471" spans="2:4">
+      <c r="B471" s="56"/>
+      <c r="D471" s="66" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="472" spans="2:4">
+      <c r="B472" s="56" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D472" s="66" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="473" spans="2:4">
+      <c r="B473" s="56"/>
+      <c r="D473" s="66" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="474" spans="2:4">
+      <c r="B474" s="56" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D474" s="66" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="475" spans="2:4">
+      <c r="B475" s="56"/>
+      <c r="D475" s="66" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="476" spans="2:4">
+      <c r="B476" s="56" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D476" s="66" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="477" spans="2:4">
+      <c r="B477" s="1"/>
+      <c r="D477" s="66" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="478" spans="2:4">
+      <c r="B478" s="1"/>
+      <c r="D478" s="66" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="479" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B479" s="1"/>
+      <c r="D479" s="66" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="480" spans="2:4" ht="32.25" thickBot="1">
+      <c r="B480" s="59" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D480" s="66" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="481" spans="2:4">
+      <c r="B481" s="1"/>
+      <c r="D481" s="1"/>
+    </row>
+    <row r="482" spans="2:4">
+      <c r="B482" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D482" s="80" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="483" spans="2:4">
+      <c r="B483" s="56"/>
+      <c r="D483" s="1"/>
+    </row>
+    <row r="484" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B484" s="56" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D484" s="81" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="485" spans="2:4">
+      <c r="B485" s="56"/>
+    </row>
+    <row r="486" spans="2:4">
+      <c r="B486" s="57" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="487" spans="2:4">
+      <c r="B487" s="56"/>
+    </row>
+    <row r="488" spans="2:4">
+      <c r="B488" s="57" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="489" spans="2:4">
+      <c r="B489" s="56"/>
+    </row>
+    <row r="490" spans="2:4">
+      <c r="B490" s="57" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="491" spans="2:4">
+      <c r="B491" s="56"/>
+    </row>
+    <row r="492" spans="2:4">
+      <c r="B492" s="57" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="493" spans="2:4">
+      <c r="B493" s="56"/>
+    </row>
+    <row r="494" spans="2:4">
+      <c r="B494" s="56" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="495" spans="2:4">
+      <c r="B495" s="56"/>
+    </row>
+    <row r="496" spans="2:4">
+      <c r="B496" s="56" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="56"/>
+    </row>
+    <row r="498" spans="2:2">
+      <c r="B498" s="56" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="499" spans="2:2">
+      <c r="B499" s="56"/>
+    </row>
+    <row r="500" spans="2:2">
+      <c r="B500" s="56" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="501" spans="2:2">
+      <c r="B501" s="56"/>
+    </row>
+    <row r="502" spans="2:2">
+      <c r="B502" s="56" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="503" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B503" s="1"/>
+    </row>
+    <row r="504" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B504" s="59" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="505" spans="2:2">
+      <c r="B505" s="56"/>
+    </row>
+    <row r="506" spans="2:2">
+      <c r="B506" s="56" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="507" spans="2:2">
+      <c r="B507" s="56"/>
+    </row>
+    <row r="508" spans="2:2">
+      <c r="B508" s="56" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="509" spans="2:2">
+      <c r="B509" s="56"/>
+    </row>
+    <row r="510" spans="2:2">
+      <c r="B510" s="56" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="511" spans="2:2">
+      <c r="B511" s="56"/>
+    </row>
+    <row r="512" spans="2:2">
+      <c r="B512" s="56" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="513" spans="2:2">
+      <c r="B513" s="56"/>
+    </row>
+    <row r="514" spans="2:2">
+      <c r="B514" s="56" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="515" spans="2:2">
+      <c r="B515" s="56"/>
+    </row>
+    <row r="516" spans="2:2">
+      <c r="B516" s="56" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="517" spans="2:2">
+      <c r="B517" s="56"/>
+    </row>
+    <row r="518" spans="2:2">
+      <c r="B518" s="56" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="519" spans="2:2">
+      <c r="B519" s="56"/>
+    </row>
+    <row r="520" spans="2:2">
+      <c r="B520" s="56" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="521" spans="2:2">
+      <c r="B521" s="56"/>
+    </row>
+    <row r="522" spans="2:2">
+      <c r="B522" s="56" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="523" spans="2:2">
+      <c r="B523" s="56"/>
+    </row>
+    <row r="524" spans="2:2">
+      <c r="B524" s="56" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="525" spans="2:2">
+      <c r="B525" s="56"/>
+    </row>
+    <row r="526" spans="2:2">
+      <c r="B526" s="56" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="527" spans="2:2">
+      <c r="B527" s="56"/>
+    </row>
+    <row r="528" spans="2:2">
+      <c r="B528" s="56" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="529" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B529" s="1"/>
+    </row>
+    <row r="530" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B530" s="59" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="531" spans="2:2">
+      <c r="B531" s="56"/>
+    </row>
+    <row r="532" spans="2:2">
+      <c r="B532" s="56" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="533" spans="2:2">
+      <c r="B533" s="56"/>
+    </row>
+    <row r="534" spans="2:2">
+      <c r="B534" s="56" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="535" spans="2:2">
+      <c r="B535" s="56"/>
+    </row>
+    <row r="536" spans="2:2">
+      <c r="B536" s="56" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="537" spans="2:2">
+      <c r="B537" s="56"/>
+    </row>
+    <row r="538" spans="2:2">
+      <c r="B538" s="56" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="539" spans="2:2">
+      <c r="B539" s="56"/>
+    </row>
+    <row r="540" spans="2:2">
+      <c r="B540" s="56" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="541" spans="2:2">
+      <c r="B541" s="56"/>
+    </row>
+    <row r="542" spans="2:2">
+      <c r="B542" s="56" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="543" spans="2:2">
+      <c r="B543" s="56"/>
+    </row>
+    <row r="544" spans="2:2">
+      <c r="B544" s="56" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="545" spans="2:2">
+      <c r="B545" s="56"/>
+    </row>
+    <row r="546" spans="2:2">
+      <c r="B546" s="56" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="547" spans="2:2">
+      <c r="B547" s="56"/>
+    </row>
+    <row r="548" spans="2:2">
+      <c r="B548" s="56" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="549" spans="2:2">
+      <c r="B549" s="56"/>
+    </row>
+    <row r="550" spans="2:2">
+      <c r="B550" s="56" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="551" spans="2:2">
+      <c r="B551" s="56"/>
+    </row>
+    <row r="552" spans="2:2">
+      <c r="B552" s="56" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="553" spans="2:2">
+      <c r="B553" s="56"/>
+    </row>
+    <row r="554" spans="2:2">
+      <c r="B554" s="56" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="555" spans="2:2">
+      <c r="B555" s="56"/>
+    </row>
+    <row r="556" spans="2:2">
+      <c r="B556" s="57" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="557" spans="2:2">
+      <c r="B557" s="56"/>
+    </row>
+    <row r="558" spans="2:2">
+      <c r="B558" s="56" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="559" spans="2:2">
+      <c r="B559" s="1"/>
+    </row>
+    <row r="560" spans="2:2" ht="31.5">
+      <c r="B560" s="65" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="561" spans="2:2">
+      <c r="B561" s="56"/>
+    </row>
+    <row r="562" spans="2:2">
+      <c r="B562" s="56" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="563" spans="2:2">
+      <c r="B563" s="56"/>
+    </row>
+    <row r="564" spans="2:2">
+      <c r="B564" s="56" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="565" spans="2:2">
+      <c r="B565" s="56"/>
+    </row>
+    <row r="566" spans="2:2">
+      <c r="B566" s="56" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="567" spans="2:2">
+      <c r="B567" s="56"/>
+    </row>
+    <row r="568" spans="2:2">
+      <c r="B568" s="56" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="569" spans="2:2">
+      <c r="B569" s="56"/>
+    </row>
+    <row r="570" spans="2:2">
+      <c r="B570" s="56" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="571" spans="2:2">
+      <c r="B571" s="56"/>
+    </row>
+    <row r="572" spans="2:2">
+      <c r="B572" s="56" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="573" spans="2:2">
+      <c r="B573" s="56"/>
+    </row>
+    <row r="574" spans="2:2">
+      <c r="B574" s="56" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="575" spans="2:2">
+      <c r="B575" s="56"/>
+    </row>
+    <row r="576" spans="2:2">
+      <c r="B576" s="56" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="577" spans="2:2">
+      <c r="B577" s="56"/>
+    </row>
+    <row r="578" spans="2:2">
+      <c r="B578" s="56" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="579" spans="2:2">
+      <c r="B579" s="56"/>
+    </row>
+    <row r="580" spans="2:2">
+      <c r="B580" s="56" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="581" spans="2:2">
+      <c r="B581" s="56"/>
+    </row>
+    <row r="582" spans="2:2">
+      <c r="B582" s="56" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="583" spans="2:2">
+      <c r="B583" s="56"/>
+    </row>
+    <row r="584" spans="2:2">
+      <c r="B584" s="56" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="585" spans="2:2">
+      <c r="B585" s="56"/>
+    </row>
+    <row r="586" spans="2:2">
+      <c r="B586" s="56" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="587" spans="2:2">
+      <c r="B587" s="56"/>
+    </row>
+    <row r="588" spans="2:2">
+      <c r="B588" s="56" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="589" spans="2:2">
+      <c r="B589" s="56"/>
+    </row>
+    <row r="590" spans="2:2">
+      <c r="B590" s="56" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="591" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B591" s="1"/>
+    </row>
+    <row r="592" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B592" s="59" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="593" spans="2:2">
+      <c r="B593" s="56"/>
+    </row>
+    <row r="594" spans="2:2">
+      <c r="B594" s="56" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="595" spans="2:2">
+      <c r="B595" s="56"/>
+    </row>
+    <row r="596" spans="2:2">
+      <c r="B596" s="57" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="597" spans="2:2">
+      <c r="B597" s="56"/>
+    </row>
+    <row r="598" spans="2:2">
+      <c r="B598" s="57" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="599" spans="2:2">
+      <c r="B599" s="56"/>
+    </row>
+    <row r="600" spans="2:2">
+      <c r="B600" s="57" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="601" spans="2:2">
+      <c r="B601" s="56"/>
+    </row>
+    <row r="602" spans="2:2">
+      <c r="B602" s="57" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="603" spans="2:2">
+      <c r="B603" s="56"/>
+    </row>
+    <row r="604" spans="2:2">
+      <c r="B604" s="57" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="605" spans="2:2">
+      <c r="B605" s="56"/>
+    </row>
+    <row r="606" spans="2:2">
+      <c r="B606" s="57" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="607" spans="2:2">
+      <c r="B607" s="56"/>
+    </row>
+    <row r="608" spans="2:2">
+      <c r="B608" s="57" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="609" spans="2:2">
+      <c r="B609" s="56"/>
+    </row>
+    <row r="610" spans="2:2">
+      <c r="B610" s="57" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="611" spans="2:2">
+      <c r="B611" s="56"/>
+    </row>
+    <row r="612" spans="2:2">
+      <c r="B612" s="57" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="613" spans="2:2">
+      <c r="B613" s="56"/>
+    </row>
+    <row r="614" spans="2:2">
+      <c r="B614" s="57" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="615" spans="2:2">
+      <c r="B615" s="1"/>
+    </row>
+    <row r="616" spans="2:2">
+      <c r="B616" s="1" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="617" spans="2:2">
+      <c r="B617" s="56"/>
+    </row>
+    <row r="618" spans="2:2">
+      <c r="B618" s="56" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="619" spans="2:2">
+      <c r="B619" s="56"/>
+    </row>
+    <row r="620" spans="2:2">
+      <c r="B620" s="56" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="621" spans="2:2">
+      <c r="B621" s="56"/>
+    </row>
+    <row r="622" spans="2:2">
+      <c r="B622" s="56" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="623" spans="2:2">
+      <c r="B623" s="56"/>
+    </row>
+    <row r="624" spans="2:2">
+      <c r="B624" s="56" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="625" spans="2:2">
+      <c r="B625" s="56"/>
+    </row>
+    <row r="626" spans="2:2">
+      <c r="B626" s="56" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="627" spans="2:2">
+      <c r="B627" s="56"/>
+    </row>
+    <row r="628" spans="2:2">
+      <c r="B628" s="56" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="629" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B629" s="1"/>
+    </row>
+    <row r="630" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B630" s="59" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="631" spans="2:2">
+      <c r="B631" s="56"/>
+    </row>
+    <row r="632" spans="2:2">
+      <c r="B632" s="56" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="633" spans="2:2">
+      <c r="B633" s="56"/>
+    </row>
+    <row r="634" spans="2:2">
+      <c r="B634" s="56" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="635" spans="2:2">
+      <c r="B635" s="56"/>
+    </row>
+    <row r="636" spans="2:2">
+      <c r="B636" s="56" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="637" spans="2:2">
+      <c r="B637" s="56"/>
+    </row>
+    <row r="638" spans="2:2">
+      <c r="B638" s="56" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="639" spans="2:2">
+      <c r="B639" s="56"/>
+    </row>
+    <row r="640" spans="2:2">
+      <c r="B640" s="56" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="641" spans="2:2">
+      <c r="B641" s="56"/>
+    </row>
+    <row r="642" spans="2:2">
+      <c r="B642" s="56" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="643" spans="2:2">
+      <c r="B643" s="56"/>
+    </row>
+    <row r="644" spans="2:2">
+      <c r="B644" s="56" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="645" spans="2:2">
+      <c r="B645" s="56"/>
+    </row>
+    <row r="646" spans="2:2">
+      <c r="B646" s="56" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="647" spans="2:2">
+      <c r="B647" s="56"/>
+    </row>
+    <row r="648" spans="2:2">
+      <c r="B648" s="56" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="649" spans="2:2">
+      <c r="B649" s="56"/>
+    </row>
+    <row r="650" spans="2:2">
+      <c r="B650" s="56" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="651" spans="2:2">
+      <c r="B651" s="56"/>
+    </row>
+    <row r="652" spans="2:2">
+      <c r="B652" s="56" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="653" spans="2:2">
+      <c r="B653" s="56"/>
+    </row>
+    <row r="654" spans="2:2">
+      <c r="B654" s="56" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="655" spans="2:2">
+      <c r="B655" s="56"/>
+    </row>
+    <row r="656" spans="2:2">
+      <c r="B656" s="56" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="657" spans="2:2">
+      <c r="B657" s="56"/>
+    </row>
+    <row r="658" spans="2:2">
+      <c r="B658" s="56" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="659" spans="2:2">
+      <c r="B659" s="56"/>
+    </row>
+    <row r="660" spans="2:2">
+      <c r="B660" s="56" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="661" spans="2:2">
+      <c r="B661" s="1"/>
+    </row>
+    <row r="662" spans="2:2">
+      <c r="B662" s="1"/>
+    </row>
+    <row r="663" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B663" s="1"/>
+    </row>
+    <row r="664" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B664" s="59" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="665" spans="2:2">
+      <c r="B665" s="1"/>
+    </row>
+    <row r="666" spans="2:2">
+      <c r="B666" s="56" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="667" spans="2:2">
+      <c r="B667" s="56"/>
+    </row>
+    <row r="668" spans="2:2">
+      <c r="B668" s="57" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="669" spans="2:2">
+      <c r="B669" s="56"/>
+    </row>
+    <row r="670" spans="2:2">
+      <c r="B670" s="57" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="671" spans="2:2">
+      <c r="B671" s="56"/>
+    </row>
+    <row r="672" spans="2:2">
+      <c r="B672" s="57" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="673" spans="2:2">
+      <c r="B673" s="56"/>
+    </row>
+    <row r="674" spans="2:2">
+      <c r="B674" s="57" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="675" spans="2:2">
+      <c r="B675" s="56"/>
+    </row>
+    <row r="676" spans="2:2">
+      <c r="B676" s="56" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="677" spans="2:2">
+      <c r="B677" s="56"/>
+    </row>
+    <row r="678" spans="2:2">
+      <c r="B678" s="56" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="679" spans="2:2">
+      <c r="B679" s="56"/>
+    </row>
+    <row r="680" spans="2:2">
+      <c r="B680" s="56" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="681" spans="2:2">
+      <c r="B681" s="56"/>
+    </row>
+    <row r="682" spans="2:2">
+      <c r="B682" s="56" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="683" spans="2:2">
+      <c r="B683" s="56"/>
+    </row>
+    <row r="684" spans="2:2">
+      <c r="B684" s="57" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="685" spans="2:2">
+      <c r="B685" s="56"/>
+    </row>
+    <row r="686" spans="2:2">
+      <c r="B686" s="56" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="687" spans="2:2">
+      <c r="B687" s="56"/>
+    </row>
+    <row r="688" spans="2:2">
+      <c r="B688" s="57" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="689" spans="2:2">
+      <c r="B689" s="56"/>
+    </row>
+    <row r="690" spans="2:2">
+      <c r="B690" s="56" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="691" spans="2:2">
+      <c r="B691" s="56"/>
+    </row>
+    <row r="692" spans="2:2">
+      <c r="B692" s="57" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="693" spans="2:2">
+      <c r="B693" s="56"/>
+    </row>
+    <row r="694" spans="2:2">
+      <c r="B694" s="56" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="695" spans="2:2">
+      <c r="B695" s="56"/>
+    </row>
+    <row r="696" spans="2:2">
+      <c r="B696" s="56" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="697" spans="2:2">
+      <c r="B697" s="56"/>
+    </row>
+    <row r="698" spans="2:2">
+      <c r="B698" s="56" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="699" spans="2:2">
+      <c r="B699" s="56"/>
+    </row>
+    <row r="700" spans="2:2">
+      <c r="B700" s="56" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="701" spans="2:2">
+      <c r="B701" s="56"/>
+    </row>
+    <row r="702" spans="2:2">
+      <c r="B702" s="56" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="703" spans="2:2">
+      <c r="B703" s="56"/>
+    </row>
+    <row r="704" spans="2:2">
+      <c r="B704" s="56" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="705" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B705" s="1"/>
+    </row>
+    <row r="706" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B706" s="59" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="707" spans="2:2">
+      <c r="B707" s="1"/>
+    </row>
+    <row r="708" spans="2:2">
+      <c r="B708" s="1" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="709" spans="2:2">
+      <c r="B709" s="56"/>
+    </row>
+    <row r="710" spans="2:2">
+      <c r="B710" s="56" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="711" spans="2:2">
+      <c r="B711" s="56"/>
+    </row>
+    <row r="712" spans="2:2">
+      <c r="B712" s="56" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="713" spans="2:2">
+      <c r="B713" s="56"/>
+    </row>
+    <row r="714" spans="2:2">
+      <c r="B714" s="56" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="715" spans="2:2">
+      <c r="B715" s="56"/>
+    </row>
+    <row r="716" spans="2:2">
+      <c r="B716" s="56" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="717" spans="2:2">
+      <c r="B717" s="56"/>
+    </row>
+    <row r="718" spans="2:2">
+      <c r="B718" s="56" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="719" spans="2:2">
+      <c r="B719" s="56"/>
+    </row>
+    <row r="720" spans="2:2">
+      <c r="B720" s="56" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="721" spans="2:2">
+      <c r="B721" s="56"/>
+    </row>
+    <row r="722" spans="2:2">
+      <c r="B722" s="56" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="723" spans="2:2">
+      <c r="B723" s="56"/>
+    </row>
+    <row r="724" spans="2:2">
+      <c r="B724" s="56" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="725" spans="2:2">
+      <c r="B725" s="56"/>
+    </row>
+    <row r="726" spans="2:2">
+      <c r="B726" s="56" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="727" spans="2:2">
+      <c r="B727" s="56"/>
+    </row>
+    <row r="728" spans="2:2">
+      <c r="B728" s="56" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="729" spans="2:2">
+      <c r="B729" s="56"/>
+    </row>
+    <row r="730" spans="2:2">
+      <c r="B730" s="56" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="731" spans="2:2">
+      <c r="B731" s="56"/>
+    </row>
+    <row r="732" spans="2:2">
+      <c r="B732" s="56" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="733" spans="2:2">
+      <c r="B733" s="56"/>
+    </row>
+    <row r="734" spans="2:2">
+      <c r="B734" s="56" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="735" spans="2:2">
+      <c r="B735" s="56"/>
+    </row>
+    <row r="736" spans="2:2">
+      <c r="B736" s="56" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="737" spans="2:2">
+      <c r="B737" s="56"/>
+    </row>
+    <row r="738" spans="2:2">
+      <c r="B738" s="56" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="739" spans="2:2">
+      <c r="B739" s="56"/>
+    </row>
+    <row r="740" spans="2:2">
+      <c r="B740" s="56" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="741" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B741" s="1"/>
+    </row>
+    <row r="742" spans="2:2" ht="32.25" thickBot="1">
+      <c r="B742" s="59" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="743" spans="2:2">
+      <c r="B743" s="56"/>
+    </row>
+    <row r="744" spans="2:2">
+      <c r="B744" s="56" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="745" spans="2:2">
+      <c r="B745" s="56"/>
+    </row>
+    <row r="746" spans="2:2">
+      <c r="B746" s="56" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="747" spans="2:2">
+      <c r="B747" s="56"/>
+    </row>
+    <row r="748" spans="2:2">
+      <c r="B748" s="56" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="749" spans="2:2">
+      <c r="B749" s="56"/>
+    </row>
+    <row r="750" spans="2:2">
+      <c r="B750" s="56" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="751" spans="2:2">
+      <c r="B751" s="56"/>
+    </row>
+    <row r="752" spans="2:2">
+      <c r="B752" s="56" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="753" spans="2:2">
+      <c r="B753" s="56"/>
+    </row>
+    <row r="754" spans="2:2">
+      <c r="B754" s="56" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="755" spans="2:2">
+      <c r="B755" s="56"/>
+    </row>
+    <row r="756" spans="2:2">
+      <c r="B756" s="56" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="757" spans="2:2">
+      <c r="B757" s="56"/>
+    </row>
+    <row r="758" spans="2:2">
+      <c r="B758" s="56" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="759" spans="2:2">
+      <c r="B759" s="56"/>
+    </row>
+    <row r="760" spans="2:2">
+      <c r="B760" s="56" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="761" spans="2:2">
+      <c r="B761" s="56"/>
+    </row>
+    <row r="762" spans="2:2">
+      <c r="B762" s="56" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="763" spans="2:2">
+      <c r="B763" s="56"/>
+    </row>
+    <row r="764" spans="2:2">
+      <c r="B764" s="56" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="765" spans="2:2">
+      <c r="B765" s="56"/>
+    </row>
+    <row r="766" spans="2:2">
+      <c r="B766" s="56" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="767" spans="2:2">
+      <c r="B767" s="56"/>
+    </row>
+    <row r="768" spans="2:2">
+      <c r="B768" s="56" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="769" spans="2:2">
+      <c r="B769" s="56"/>
+    </row>
+    <row r="770" spans="2:2">
+      <c r="B770" s="56" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="771" spans="2:2">
+      <c r="B771" s="56"/>
+    </row>
+    <row r="772" spans="2:2">
+      <c r="B772" s="56" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="773" spans="2:2">
+      <c r="B773" s="56"/>
+    </row>
+    <row r="774" spans="2:2">
+      <c r="B774" s="56" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="775" spans="2:2">
+      <c r="B775" s="56"/>
+    </row>
+    <row r="776" spans="2:2">
+      <c r="B776" s="56" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="777" spans="2:2">
+      <c r="B777" s="56"/>
+    </row>
+    <row r="778" spans="2:2">
+      <c r="B778" s="56" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="779" spans="2:2">
+      <c r="B779" s="56"/>
+    </row>
+    <row r="780" spans="2:2">
+      <c r="B780" s="56" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="781" spans="2:2">
+      <c r="B781" s="56"/>
+    </row>
+    <row r="782" spans="2:2">
+      <c r="B782" s="56" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="783" spans="2:2">
+      <c r="B783" s="1"/>
+    </row>
+    <row r="784" spans="2:2">
+      <c r="B784" s="1"/>
+    </row>
+    <row r="785" spans="2:2">
+      <c r="B785" s="1"/>
+    </row>
+    <row r="786" spans="2:2" ht="31.5">
+      <c r="B786" s="65" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="787" spans="2:2">
+      <c r="B787" s="1"/>
+    </row>
+    <row r="788" spans="2:2" ht="18">
+      <c r="B788" s="55" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="789" spans="2:2">
+      <c r="B789" s="1"/>
+    </row>
+    <row r="790" spans="2:2">
+      <c r="B790" s="66" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="791" spans="2:2">
+      <c r="B791" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="792" spans="2:2">
+      <c r="B792" s="66" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="793" spans="2:2">
+      <c r="B793" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="794" spans="2:2">
+      <c r="B794" s="66" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="795" spans="2:2">
+      <c r="B795" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="796" spans="2:2">
+      <c r="B796" s="66" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="797" spans="2:2">
+      <c r="B797" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="798" spans="2:2">
+      <c r="B798" s="66" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="799" spans="2:2">
+      <c r="B799" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="800" spans="2:2">
+      <c r="B800" s="66" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="801" spans="2:2">
+      <c r="B801" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="802" spans="2:2">
+      <c r="B802" s="66" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="803" spans="2:2">
+      <c r="B803" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="804" spans="2:2">
+      <c r="B804" s="66" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="805" spans="2:2">
+      <c r="B805" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="806" spans="2:2">
+      <c r="B806" s="66" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="807" spans="2:2">
+      <c r="B807" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="808" spans="2:2">
+      <c r="B808" s="66" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="809" spans="2:2">
+      <c r="B809" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="810" spans="2:2">
+      <c r="B810" s="66" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="811" spans="2:2">
+      <c r="B811" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="812" spans="2:2">
+      <c r="B812" s="66" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="813" spans="2:2">
+      <c r="B813" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="814" spans="2:2">
+      <c r="B814" s="66" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="815" spans="2:2">
+      <c r="B815" s="66" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="816" spans="2:2">
+      <c r="B816" s="66" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="817" spans="2:2">
+      <c r="B817" s="1"/>
+    </row>
+    <row r="818" spans="2:2" ht="18">
+      <c r="B818" s="61" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="819" spans="2:2">
+      <c r="B819" s="1"/>
+    </row>
+    <row r="820" spans="2:2">
+      <c r="B820" s="66" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="821" spans="2:2">
+      <c r="B821" s="66" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="822" spans="2:2">
+      <c r="B822" s="66" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="823" spans="2:2">
+      <c r="B823" s="66" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="824" spans="2:2">
+      <c r="B824" s="66" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="825" spans="2:2">
+      <c r="B825" s="66" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="826" spans="2:2">
+      <c r="B826" s="66" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="827" spans="2:2">
+      <c r="B827" s="66" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="828" spans="2:2">
+      <c r="B828" s="66" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="829" spans="2:2">
+      <c r="B829" s="66" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="830" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B830" s="1"/>
+    </row>
+    <row r="831" spans="2:2" ht="18.75" thickBot="1">
+      <c r="B831" s="60" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="832" spans="2:2">
+      <c r="B832" s="1"/>
+    </row>
+    <row r="833" spans="2:2">
+      <c r="B833" s="66" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="834" spans="2:2">
+      <c r="B834" s="66" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="835" spans="2:2">
+      <c r="B835" s="66" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="836" spans="2:2">
+      <c r="B836" s="66" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="837" spans="2:2">
+      <c r="B837" s="66" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="838" spans="2:2">
+      <c r="B838" s="66" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="839" spans="2:2">
+      <c r="B839" s="66" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="840" spans="2:2">
+      <c r="B840" s="66" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="841" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B841" s="67" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="842" spans="2:2">
+      <c r="B842" s="1"/>
+    </row>
+    <row r="843" spans="2:2">
+      <c r="B843" s="43" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="844" spans="2:2" ht="15.75" thickBot="1">
+      <c r="B844" s="44" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" tooltip="SQL 50 - Study Plan - LeetCode" display="https://leetcode.com/studyplan/top-sql-50/?trk=public_profile_certification-title&amp;utm_source=chatgpt.com" xr:uid="{5B19D161-06EB-4212-BCE9-3A42A51D57A4}"/>
+    <hyperlink ref="D3" r:id="rId2" tooltip="Database SQL Primer (Part 1) [ Overview | Query Execution Order | References ] - Discuss - LeetCode" display="https://leetcode.com/discuss/post/1600718/database-sql-primer-part-1-overview-query-execution-order-references/?utm_source=chatgpt.com" xr:uid="{57BE98AF-CD28-4847-B519-E5B4A93F5E26}"/>
+    <hyperlink ref="D482" r:id="rId3" tooltip="SQL database - LeetCode" display="https://leetcode.com/problem-list/e97a9e5m/?utm_source=chatgpt.com" xr:uid="{4823DB0A-9B61-4013-AAC7-39C0B1EF78FF}"/>
+    <hyperlink ref="D484" r:id="rId4" tooltip="SQL 50 - Study Plan - LeetCode" display="https://leetcode.com/studyplan/top-sql-50/?trk=public_profile_certification-title&amp;utm_source=chatgpt.com" xr:uid="{E5F40C2D-4A26-4665-A7CC-93D768B11623}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD1711C-57F5-4E6D-A25C-CF0B192DC035}">
   <dimension ref="B3:B428"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23074,667 +30378,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638825F5-223F-4189-9563-B7916650E823}">
-  <dimension ref="A2:A167"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="71" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="28" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="28" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="28" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="28" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="28" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="28" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="28" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="28" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="28" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="28" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="28" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="28" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="28" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="28" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="28" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="28" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="28" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="28" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="28" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="28" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="28" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="28" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="28" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="28" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="28" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="28" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="28" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="28" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="28" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="28" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="28" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="28" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="28" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="28" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="28" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="28" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="28" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="28" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>364</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>